--- a/weeks/2026-09-03/巡查表.xlsx
+++ b/weeks/2026-09-03/巡查表.xlsx
@@ -657,9 +657,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O3">
+      <c r="O3" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91_%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91.html","查看证据(4项/10张)")</f>
-        <v/>
+        <v>查看证据(4项/10张)</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -773,9 +773,9 @@
           <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O4">
+      <c r="O4" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E6%98%9F%E6%B2%B3%E4%BC%A0%E5%A5%87_%E6%98%9F%E6%B2%B3%E4%BC%A0%E5%A5%87.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -890,9 +890,9 @@
 4.1: 不得主动向消费者提供客房一次性日用品。（10分） (-10)</t>
         </is>
       </c>
-      <c r="O5">
+      <c r="O5" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E6%9D%BE%E4%BB%94%E5%9B%AD%E7%BB%B4%E4%B9%9F%E7%BA%B3%E9%85%92%E5%BA%97_%E9%BE%99%E5%8D%8E%E4%BA%BA%E6%B0%91%E5%8D%97%E8%B7%AF%E5%BA%97_%E6%B7%B1%E5%9C%B3%E5%B8%82%E6%82%A6%E7%BE%8E%E4%BD%B3%E9%85%92%E5%BA%97%E7%AE%A1%E7%90%86%E6%9C%89%E9%99%90%E5%85%AC%E5%8F%B8_%E7%BB%B4%E4%B9%9F%E7%BA%B3%E4%BA%BA%E6%B0%91%E5%8D%97%E8%B7%AF%E5%BA%97_.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1006,9 +1006,9 @@
           <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O6">
+      <c r="O6" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E8%8E%B1%E8%92%99_%E6%B0%B4%E6%A6%AD%E6%98%A5%E5%A4%A9_%E6%B0%B4%E6%A6%AD%E6%98%A5%E5%A4%A9%E8%8A%B1%E5%9B%AD.html","查看证据(1项/3张)")</f>
-        <v/>
+        <v>查看证据(1项/3张)</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1125,9 +1125,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O7">
+      <c r="O7" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E8%85%BE%E9%BE%99%E8%B7%AF124%E5%A4%A9%E8%99%B9%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83_%E9%BE%99%E5%8D%8E%E5%BA%97_%E4%B8%AD%E8%88%AA%E5%A4%A9%E9%80%B8%E7%AE%A1%E7%90%86%E5%A4%84.html","查看证据(4项/13张)")</f>
-        <v/>
+        <v>查看证据(4项/13张)</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,9 +1241,9 @@
           <t>2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O8">
+      <c r="O8" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E4%B8%9C%E9%83%BD%E9%9B%85%E8%8B%91%E9%B9%8F%E5%8D%8E%E4%B8%96%E5%AE%B6%E5%8D%8E%E5%BA%9C_%E9%B9%8F%E5%8D%8E%E4%B8%96%E5%AE%B6.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,9 +1357,9 @@
           <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O9">
+      <c r="O9" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E7%89%B9%E5%8A%9B%E5%95%86%E5%8E%A6_%E7%89%B9%E5%8A%9B%E5%95%86%E5%8E%A6.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1474,9 +1474,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O10">
+      <c r="O10" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%8E%E4%B8%9A%E5%A4%A7%E5%A4%8F_%E6%B7%B1%E5%8D%8E%E4%B8%9A%E5%A4%A7%E5%8E%A6.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1595,9 +1595,9 @@
           <t>1.6: 各类收集容器的分类标志完整、正确、清晰。 （12分） (-3)</t>
         </is>
       </c>
-      <c r="O11">
+      <c r="O11" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E6%96%B0%E5%9B%AD%E8%B7%AF89%E5%8F%B7_%E4%B8%AD%E5%BF%83%E5%B9%BC%E5%84%BF%E5%9B%AD.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1717,9 +1717,9 @@
 4.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O12">
+      <c r="O12" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E7%9F%B3%E6%99%AF%E8%8A%B1%E5%9B%AD_%E5%BA%94%E4%BA%BA%E7%9F%B3%E7%9F%B3%E6%99%AF%E5%B0%8F%E5%8C%BA.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1835,9 +1835,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O13">
+      <c r="O13" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E5%B9%B3%E6%B9%96%E8%8A%B1%E5%9B%AD_%E5%B9%B3%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1958,9 +1958,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)</t>
         </is>
       </c>
-      <c r="O14">
+      <c r="O14" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据(8项/16张)")</f>
-        <v/>
+        <v>查看证据(8项/16张)</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -2075,9 +2075,9 @@
 1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O15">
+      <c r="O15" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E9%94%A6%E5%86%A0%E5%8D%8E%E5%BA%AD_%E9%94%A6%E5%86%A0%E5%8D%8E%E5%BA%AD.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2193,9 +2193,9 @@
 4.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O16">
+      <c r="O16" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E5%8F%88%E4%B8%80%E6%9D%91_%E5%A1%98%E5%A4%B4%E5%8F%88%E4%B8%80%E6%9D%91.html","查看证据(3项/7张)")</f>
-        <v/>
+        <v>查看证据(3项/7张)</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -2311,9 +2311,9 @@
 2.2: 收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。 (-3)</t>
         </is>
       </c>
-      <c r="O17">
+      <c r="O17" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E8%A3%95%E5%92%8C%E5%8D%97%E8%A1%972_38%E5%8F%B7_%E8%8D%94%E5%9B%AD%E5%B8%82%E5%9C%BA.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -2429,9 +2429,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O18">
+      <c r="O18" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF7022%E5%8F%B7_%E9%B2%81%E7%8F%AD%E5%A4%A7%E5%8E%A6.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2547,9 +2547,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O19">
+      <c r="O19" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF7024%E5%8F%B7_%E5%B8%82%E6%94%BF%E5%A4%A7%E9%99%A2.html","查看证据(3项/6张)")</f>
-        <v/>
+        <v>查看证据(3项/6张)</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2670,9 +2670,9 @@
 6.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O20">
+      <c r="O20" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF77%E5%8F%B7_%E6%93%8E%E5%A4%A9%E5%8D%8E%E5%BA%AD.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2794,9 +2794,9 @@
 6.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O21">
+      <c r="O21" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%95%86%E6%8A%A5%E8%B7%AF18%E5%8F%B7_%E7%BF%A0%E6%99%AF%E5%9B%AD.html","查看证据(4项/5张)")</f>
-        <v/>
+        <v>查看证据(4项/5张)</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2914,9 +2914,9 @@
 3.1: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O22">
+      <c r="O22" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7_%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD.html","查看证据(5项/11张)")</f>
-        <v/>
+        <v>查看证据(5项/11张)</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -3030,9 +3030,9 @@
           <t>1.6: 各类收集容器的分类标志完整、正确、清晰。 （12分） (-3)</t>
         </is>
       </c>
-      <c r="O23">
+      <c r="O23" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%95%BF%E5%B2%AD%E8%B7%AF13_2_%E9%95%BF%E5%B2%AD%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -3147,9 +3147,9 @@
 1.3: 各类收集容器的分类标志完整、正确、清晰。 （18分） (-3)</t>
         </is>
       </c>
-      <c r="O24">
+      <c r="O24" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD%E4%B8%9C%E9%97%A8%E9%99%A2%E5%86%85101_%E5%8E%9F%E6%B1%81%E5%8E%9F%E5%91%B3%E9%A9%B4%E5%BA%84%E9%A4%90%E5%8E%85.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -3267,9 +3267,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O25">
+      <c r="O25" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E8%8E%B2%E8%8A%B1%E8%B7%AF2069%E5%8F%B7_%E6%99%AF%E7%94%B0%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C180%E7%B1%B3_%E7%BC%94%E6%A2%A6%E5%9B%AD.html","查看证据(5项/8张)")</f>
-        <v/>
+        <v>查看证据(5项/8张)</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -3384,9 +3384,9 @@
 1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O26">
+      <c r="O26" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2008%E5%8F%B7_%E8%88%AA%E5%A4%A9%E6%99%B4%E5%B1%B1%E6%9C%88%E5%90%8D%E5%9B%AD.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -3506,9 +3506,9 @@
 3.1: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O27">
+      <c r="O27" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B2%99%E8%B7%AF2068%E5%8F%B7%E7%8E%89%E9%9B%85%E5%B1%85_%E7%8E%89%E9%9B%85%E5%B1%85.html","查看证据(2项/4张)")</f>
-        <v/>
+        <v>查看证据(2项/4张)</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -3633,9 +3633,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O28">
+      <c r="O28" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E8%8E%B2%E5%A1%98%E8%A1%97%E9%81%93%E4%B8%83%E5%8F%B7%E8%B7%AF2%E5%8F%B7_%E5%85%AC%E4%BA%A4%E6%A2%A7%E6%A1%90%E8%8B%91.html","查看证据(7项/8张)")</f>
-        <v/>
+        <v>查看证据(7项/8张)</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -3754,9 +3754,9 @@
           <t>2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O29">
+      <c r="O29" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0366%E5%8F%B7_%E5%B1%B1%E6%B0%B4%E6%83%85%E5%AE%B6%E5%9B%AD.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -3876,9 +3876,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O30">
+      <c r="O30" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0308%E5%8F%B7_%E5%A4%AA%E5%AD%90%E5%B1%B1%E5%BA%84.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -3998,9 +3998,9 @@
 1.6: 各类收集容器的分类标志完整、正确、清晰。 (-3)</t>
         </is>
       </c>
-      <c r="O31">
+      <c r="O31" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%A5%BF%E8%B7%AF%E5%92%8C%E6%99%AF%E7%94%B0%E8%A5%BF%E4%BA%8C%E8%A1%97%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%A4%A9%E5%81%A5%E5%A4%A9%E9%AA%84%E5%85%AC%E4%BA%A4%E9%A6%96%E6%9C%AB%E7%AB%99.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -4119,9 +4119,9 @@
           <t>2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O32">
+      <c r="O32" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0308%E5%8F%B7_%E5%B1%B1%E5%B1%85%E5%B2%81%E6%9C%88.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -4243,9 +4243,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O33">
+      <c r="O33" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF83%E5%8F%B7_%E4%B8%87%E6%89%98%E5%AE%B6%E5%9B%AD.html","查看证据(4项/6张)")</f>
-        <v/>
+        <v>查看证据(4项/6张)</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -4364,9 +4364,9 @@
 6.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O34">
+      <c r="O34" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF81%E5%8F%B7_%E7%A2%A7%E6%99%AF%E5%9B%AD.html","查看证据(6项/7张)")</f>
-        <v/>
+        <v>查看证据(6项/7张)</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -4486,9 +4486,9 @@
 2.5: 管理维护垃圾分类设施，将环境卫生、垃圾分类等要求纳入日常巡查内容。（3分） (-3)</t>
         </is>
       </c>
-      <c r="O35">
+      <c r="O35" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C%E6%B7%B1%E5%9C%B3%E5%8D%97%E5%B1%B1%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C_%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -4604,9 +4604,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O36">
+      <c r="O36" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E4%B8%9C%E5%8C%BA_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E4%B8%9C%E5%8C%BA.html","查看证据(3项/8张)")</f>
-        <v/>
+        <v>查看证据(3项/8张)</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -4727,9 +4727,9 @@
 1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O37">
+      <c r="O37" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E9%9D%92%E9%9D%92%E8%B7%AF2%E5%8F%B7_%E9%9D%92%E9%9D%92%E5%B1%B1%E5%BA%84.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -4849,9 +4849,9 @@
 1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-5)</t>
         </is>
       </c>
-      <c r="O38">
+      <c r="O38" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E6%A8%9F%E9%98%81%E8%B7%AF329%E5%8F%B7_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E8%A5%BF%E5%8C%BA.html","查看证据(7项/17张)")</f>
-        <v/>
+        <v>查看证据(7项/17张)</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -4972,9 +4972,9 @@
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O39">
+      <c r="O39" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0369%E5%8F%B7_%E8%AF%BA%E5%BE%B7%E5%81%87%E6%97%A5%E8%8A%B1%E5%9B%AD.html","查看证据(3项/7张)")</f>
-        <v/>
+        <v>查看证据(3项/7张)</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -5094,9 +5094,9 @@
 1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-6)</t>
         </is>
       </c>
-      <c r="O40">
+      <c r="O40" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0389%E5%8F%B7_%E9%9B%B7%E5%9C%B3%E7%A2%A7%E6%A6%95%E6%B9%BE%E6%B5%B7%E6%99%AF%E8%8A%B1%E5%9B%AD.html","查看证据(2项/5张)")</f>
-        <v/>
+        <v>查看证据(2项/5张)</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -5210,9 +5210,9 @@
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O41">
+      <c r="O41" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%80%81%E5%9D%91%E4%BA%95%E6%B0%B4%E9%BE%991%E5%8F%B7_%E4%BA%95%E6%B0%B4%E9%BE%99.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -5326,9 +5326,9 @@
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O42">
+      <c r="O42" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%80%81%E5%9D%91%E4%B8%9C%E5%9D%9183%E5%8F%B7_%E4%B8%9C%E5%9D%91.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -5443,9 +5443,9 @@
 1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O43">
+      <c r="O43" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A1%98%E5%A4%B4%E5%A4%A7%E9%81%9368%E5%8F%B7_%E5%A1%98%E5%A4%B4%E6%96%B0%E6%9D%91.html","查看证据(2项/5张)")</f>
-        <v/>
+        <v>查看证据(2项/5张)</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -5567,9 +5567,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O44">
+      <c r="O44" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA%E5%A1%98%E5%A4%B4%E8%B7%AF12%E5%8F%B7%E6%97%81_%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA.html","查看证据(4项/6张)")</f>
-        <v/>
+        <v>查看证据(4项/6张)</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -5684,9 +5684,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O45">
+      <c r="O45" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B7%B1%E7%9B%90%E8%B7%AF1119%E5%8F%B7_%E6%B5%B7%E6%BB%A8%E5%81%87%E6%97%A5.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -5800,9 +5800,9 @@
           <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O46">
+      <c r="O46" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E6%B5%B7%E6%BB%A8%E5%81%87%E6%97%A5%E6%98%A5%E5%A4%A9%E6%B5%B7_%E6%98%A5%E5%A4%A9%E6%B5%B7.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -5916,9 +5916,9 @@
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O47">
+      <c r="O47" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E6%98%9F%E6%B8%AF%E5%90%8D%E8%8B%91_%E6%98%9F%E6%B8%AF%E5%90%8D%E8%8B%91.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -6032,9 +6032,9 @@
           <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O48">
+      <c r="O48" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E5%8C%97%E5%B1%B1%E9%81%93127%E5%8F%B7_%E5%90%89%E9%BA%BB%E6%B9%96%E6%9D%91.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -6149,9 +6149,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O49">
+      <c r="O49" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E5%92%8C%E4%BA%A8%E5%AE%B6%E5%AE%B6%E5%9B%AD_%E5%92%8C%E4%BA%A8%E9%9B%85%E5%9B%AD.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -6271,9 +6271,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O50">
+      <c r="O50" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%87%A4%E7%BF%94%E8%A1%9736%E5%8F%B7_%E6%B1%87%E9%94%A6%E5%90%8D%E5%9B%AD.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -6390,9 +6390,9 @@
 5.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O51">
+      <c r="O51" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1010%E5%8F%B7_%E9%94%A6%E7%BB%A3%E5%A4%A7%E5%8E%A6.html","查看证据(4项/7张)")</f>
-        <v/>
+        <v>查看证据(4项/7张)</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -6516,9 +6516,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O52">
+      <c r="O52" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1018%E5%8F%B7%E5%8C%97%E9%97%A8_%E6%B5%B7%E4%B8%BD%E5%A4%A7%E5%8E%A6.html","查看证据(6项/14张)")</f>
-        <v/>
+        <v>查看证据(6项/14张)</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -6640,9 +6640,9 @@
 5.2: 箱体外观应使用“深i回收”标识，并公示备案编号、监管电话、回收电话等信息，回收电话真实有效，提供预约回收服务。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O53">
+      <c r="O53" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1002%E5%8F%B7_%E8%BD%BB%E5%B7%A5%E5%A4%A7%E5%8E%A6.html","查看证据(4项/6张)")</f>
-        <v/>
+        <v>查看证据(4项/6张)</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -6756,9 +6756,9 @@
           <t>2.2: 收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。 (-6)</t>
         </is>
       </c>
-      <c r="O54">
+      <c r="O54" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E5%8C%97%E5%B1%B1%E5%A4%A7%E9%81%93%E5%B7%A5%E4%B8%9A%E5%8C%BA146%E5%8F%B7_%E5%8C%97%E5%B1%B1%E5%B7%A5%E4%B8%9A%E5%8C%BA.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -6884,9 +6884,9 @@
 5.2: 箱体外观应使用“深i回收”标识，并公示备案编号、监管电话、回收电话等信息，回收电话真实有效，提供预约回收服务。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O55">
+      <c r="O55" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据(8项/12张)")</f>
-        <v/>
+        <v>查看证据(8项/12张)</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -7009,9 +7009,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O56">
+      <c r="O56" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1069%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E8%A5%BF%E6%9D%91.html","查看证据(5项/7张)")</f>
-        <v/>
+        <v>查看证据(5项/7张)</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -7138,9 +7138,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O57">
+      <c r="O57" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据(9项/19张)")</f>
-        <v/>
+        <v>查看证据(9项/19张)</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -7264,9 +7264,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O58">
+      <c r="O58" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%8E%E4%B8%BD%E8%B7%AF1067%E5%8F%B7_%E9%87%91%E7%9B%BE%E8%8A%B1%E5%9B%AD.html","查看证据(6项/8张)")</f>
-        <v/>
+        <v>查看证据(6项/8张)</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -7386,9 +7386,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O59">
+      <c r="O59" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1049%E5%8F%B7%E9%99%84%E8%BF%91_1049%E5%8F%B7%E4%B8%AD%E8%A1%8C%E5%AE%BF%E8%88%8D.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -7508,9 +7508,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O60">
+      <c r="O60" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1031%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E5%B0%8F%E5%8C%BA.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -7633,9 +7633,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O61">
+      <c r="O61" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1011%E5%8F%B7_%E5%8F%8B%E8%B0%8A%E5%85%AC%E5%8F%B8%E5%AE%BF%E8%88%8D.html","查看证据(5项/6张)")</f>
-        <v/>
+        <v>查看证据(5项/6张)</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
@@ -7756,9 +7756,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O62">
+      <c r="O62" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%87%A4%E5%87%B0%E8%B7%AF166%E5%8F%B7_%E5%87%A4%E5%87%B0%E8%B7%AF166%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -7883,9 +7883,9 @@
 3.1: 用餐区张贴或摆放光盘行动、节约粮食等宣传海报或温馨提示。（5分） (-5)</t>
         </is>
       </c>
-      <c r="O63">
+      <c r="O63" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E6%8C%AF%E6%98%8E%E8%B7%AF161%E5%8F%B7%E5%9B%9B%E5%AD%A3%E6%98%9F%E5%9F%8E_%E7%B2%A4%E6%B5%B7%E6%B8%94%E6%B8%AF.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -8005,9 +8005,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O64">
+      <c r="O64" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%BA%B7%E4%B9%90%E8%B7%AF%E5%85%AC%E6%98%8E%E8%A1%97%E5%BF%83%E5%85%AC%E5%9B%AD_%E5%8D%97%E5%9B%9B%E5%B7%B7.html","查看证据(2项/4张)")</f>
-        <v/>
+        <v>查看证据(2项/4张)</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -8128,9 +8128,9 @@
 2.4: 禁止向生活垃圾收集设施投放工业固体废物。 (-6)</t>
         </is>
       </c>
-      <c r="O65">
+      <c r="O65" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E9%93%81%E7%94%B2%E7%A7%91%E6%8A%80%E5%9B%AD_%E9%93%81%E7%94%B2%E5%B7%A5%E4%B8%9A%E5%9B%AD.html","查看证据(3项/11张)")</f>
-        <v/>
+        <v>查看证据(3项/11张)</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -8260,9 +8260,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O66">
+      <c r="O66" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%85%AC%E6%98%8E%E8%A7%A3%E6%94%BE%E8%A1%97%E6%B5%B7%E4%BF%A1%E8%8A%B1%E5%9B%AD_%E5%AF%8C%E5%88%A9%E8%B7%AF_%E6%97%A7%E8%A1%97%E7%89%87%E5%8C%BA.html","查看证据(7项/14张)")</f>
-        <v/>
+        <v>查看证据(7项/14张)</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -8386,9 +8386,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O67">
+      <c r="O67" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2069%E5%8F%B7_%E9%AA%8F%E7%9A%87%E5%90%8D%E5%B1%85.html","查看证据(6项/11张)")</f>
-        <v/>
+        <v>查看证据(6项/11张)</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -8506,9 +8506,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O68">
+      <c r="O68" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2053%E5%8F%B7%E9%93%B6%E6%B3%B0%E8%8B%91_%E9%93%B6%E6%B3%B0%E8%8B%91.html","查看证据(5项/11张)")</f>
-        <v/>
+        <v>查看证据(5项/11张)</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -8632,9 +8632,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O69">
+      <c r="O69" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%8F%A9%E6%8F%90%E8%B7%AF48%E5%8F%B7_%E5%8D%97%E5%85%89%E5%90%8D%E4%BB%95%E8%8B%91.html","查看证据(6项/10张)")</f>
-        <v/>
+        <v>查看证据(6项/10张)</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -8753,9 +8753,9 @@
 5.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O70">
+      <c r="O70" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E4%BF%9D%E7%A8%8E%E5%8C%BA%E8%8F%A9%E6%8F%90%E8%B7%AF18%E5%8F%B7%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD_%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD.html","查看证据(6项/10张)")</f>
-        <v/>
+        <v>查看证据(6项/10张)</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -8878,9 +8878,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O71">
+      <c r="O71" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%A4%B4%E8%A1%97%E9%81%93%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%A6%96%E5%9F%8E_%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD.html","查看证据(5项/7张)")</f>
-        <v/>
+        <v>查看证据(5项/7张)</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -9003,9 +9003,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O72">
+      <c r="O72" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0_%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0.html","查看证据(5项/8张)")</f>
-        <v/>
+        <v>查看证据(5项/8张)</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -9119,9 +9119,9 @@
           <t>1.5: 至少设置一处有害垃圾收集容器。（5分） (5)</t>
         </is>
       </c>
-      <c r="O73">
+      <c r="O73" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%AF%94%E5%AE%9D%E4%BA%8C%E8%B7%AF83%E5%8F%B7_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -9246,9 +9246,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O74">
+      <c r="O74" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA_%E7%BA%A2%E8%8A%B1%E8%B7%AF136%E5%8F%B7_%E5%8D%97%E5%B1%B1%E8%B1%AA%E5%BA%AD.html","查看证据(7项/10张)")</f>
-        <v/>
+        <v>查看证据(7项/10张)</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -9362,9 +9362,9 @@
           <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O75">
+      <c r="O75" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E6%B0%B4%E4%B8%80%E6%9D%9111%E5%8F%B7_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E6%B0%B4%E4%B8%80%E6%9D%91.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -9478,9 +9478,9 @@
           <t>1.6: 设置洗手设施。（2分） (-1)</t>
         </is>
       </c>
-      <c r="O76">
+      <c r="O76" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E6%B0%B4%E4%BA%8C%E6%9D%9113_4%E5%8F%B7_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E6%B0%B4%E4%BA%8C%E6%9D%91.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -9602,9 +9602,9 @@
 1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O77">
+      <c r="O77" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91_%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91.html","查看证据(4项/10张)")</f>
-        <v/>
+        <v>查看证据(4项/10张)</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -9726,9 +9726,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O78">
+      <c r="O78" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E5%8D%8E%E4%B8%89%E8%B7%AF8%E5%8F%B7_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C290%E7%B1%B3_%E6%81%92%E8%BF%90%E8%B1%AA%E5%BA%AD.html","查看证据(4项/6张)")</f>
-        <v/>
+        <v>查看证据(4项/6张)</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -9850,9 +9850,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O79">
+      <c r="O79" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E7%A6%8F%E5%8D%8E3%E8%B7%AF_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C370%E7%B1%B3_%E9%87%91%E7%94%B0%E6%96%B0%E6%9D%91.html","查看证据(4项/8张)")</f>
-        <v/>
+        <v>查看证据(4项/8张)</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -9976,9 +9976,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O80">
+      <c r="O80" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%BD%A9%E7%94%B0%E8%B7%AF%E5%92%8C%E7%A6%8F%E5%8D%8E%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%BD%A9%E7%A6%8F%E5%A4%A7%E5%8E%A6%E9%99%84%E8%BF%91_%E5%B2%97%E5%8E%A6%E5%9F%8E.html","查看证据(6项/15张)")</f>
-        <v/>
+        <v>查看证据(6项/15张)</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -10094,9 +10094,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O81">
+      <c r="O81" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%B2%97%E5%8E%A6%E7%A4%BE%E5%8C%BA%E6%98%9F%E6%B2%B3%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6_%E6%98%9F%E6%B2%B3%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -10215,9 +10215,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O82">
+      <c r="O82" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%93%E4%B8%8E%E9%87%91%E7%94%B0%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E6%B7%B1%E5%9C%B3%E4%B8%AD%E5%BF%83%E5%A4%A9%E5%85%83%E5%85%AC%E5%AF%93.html","查看证据(6项/8张)")</f>
-        <v/>
+        <v>查看证据(6项/8张)</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -10341,9 +10341,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O83">
+      <c r="O83" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E9%87%91%E7%94%B0%E8%B7%AF3090%E5%8F%B7_%E4%BC%9A%E5%B1%95%E4%B8%AD%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A1%E5%8F%A3%E6%AD%A5%E8%A1%8C340%E7%B1%B3_%E7%A6%8F%E5%B2%97%E5%9B%AD%E5%A4%A7%E5%8E%A6.html","查看证据(6项/9张)")</f>
-        <v/>
+        <v>查看证据(6项/9张)</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -10457,9 +10457,9 @@
           <t>3.1: 公共区域张贴或摆放垃圾分类宣传海报或指引等。 (-5)</t>
         </is>
       </c>
-      <c r="O84">
+      <c r="O84" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -10585,9 +10585,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O85">
+      <c r="O85" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据(8项/10张)")</f>
-        <v/>
+        <v>查看证据(8项/10张)</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -10708,9 +10708,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O86">
+      <c r="O86" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E8%8A%B1%E5%9B%AD_%E6%B7%B1%E5%8D%97%E8%8A%B1%E5%9B%AD.html","查看证据(3项/7张)")</f>
-        <v/>
+        <v>查看证据(3项/7张)</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -10833,9 +10833,9 @@
 4.3: 设备齐全完好，摆放整齐有序，功能正常，外观没有严重破损，没有用电隐患。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O87">
+      <c r="O87" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91_%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91.html","查看证据(5项/7张)")</f>
-        <v/>
+        <v>查看证据(5项/7张)</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -10957,9 +10957,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O88">
+      <c r="O88" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E5%85%B4%E8%B7%AF6%E5%8F%B7%E7%A7%91%E8%8B%91%E8%A5%BF%E4%BD%8F%E5%AE%85%E5%B0%8F%E5%8C%BA_%E7%A7%91%E8%8B%91%E8%A5%BF%E5%B0%8F%E5%8C%BA.html","查看证据(4项/5张)")</f>
-        <v/>
+        <v>查看证据(4项/5张)</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -11082,9 +11082,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O89">
+      <c r="O89" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A7%91%E5%8F%91%E8%B7%AF10%E5%8F%B7_%E7%BB%B4%E7%94%A8%E7%BB%BC%E5%90%88%E6%A5%BC%E7%A7%91%E8%8B%91%E5%B1%85%E5%B0%8F%E5%8C%BA.html","查看证据(5项/7张)")</f>
-        <v/>
+        <v>查看证据(5项/7张)</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -11205,9 +11205,9 @@
 2.2: 收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。 (-3)</t>
         </is>
       </c>
-      <c r="O90">
+      <c r="O90" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E8%8B%91%E8%B7%AF16%E5%8F%B7%E4%B8%9C%E6%96%B9%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6_%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E6%96%B9%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -11328,9 +11328,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O91">
+      <c r="O91" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A4%BE%E5%8C%BA%E8%AD%A6%E5%8A%A1%E5%AE%A4%E7%A7%91%E8%8B%91%E8%8A%B1%E5%9B%AD_%E7%A7%91%E5%8D%8E%E8%B7%AF_%E7%A7%91%E8%8B%91%E4%B8%9C%E5%B0%8F%E5%8C%BA.html","查看证据(3项/5张)")</f>
-        <v/>
+        <v>查看证据(3项/5张)</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -11451,9 +11451,9 @@
 1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O92">
+      <c r="O92" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%A1%91%E8%BE%BE%E8%8B%91_%E6%A1%91%E8%BE%BE%E8%8B%91.html","查看证据(3项/6张)")</f>
-        <v/>
+        <v>查看证据(3项/6张)</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -11573,9 +11573,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O93">
+      <c r="O93" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E9%AB%98%E7%A7%91%E5%A4%A7%E9%81%9388%E5%8F%B7%E5%8D%97%E6%99%AF%E5%8D%97%E7%BA%A6%E6%96%B0%E6%9D%91_%E5%8D%97%E6%99%AF%E5%8D%97%E7%BA%A6%E6%96%B0%E6%9D%91.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -11695,9 +11695,9 @@
 3.1: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O94">
+      <c r="O94" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%91%B5%E5%8D%97%E8%B7%AF110%E7%9F%B3%E6%A1%A5%E5%A4%B4%E5%B0%8F%E5%8C%BA_%E7%9F%B3%E6%A1%A5%E5%A4%B4.html","查看证据(7项/11张)")</f>
-        <v/>
+        <v>查看证据(7项/11张)</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -11817,9 +11817,9 @@
 4.2: 箱体外观应使用“深i回收”标识，并公示备案编号、监管电话、回收电话等信息，回收电话真实有效，提供预约回收服务。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O95">
+      <c r="O95" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E8%81%94%E5%92%8C%E5%8A%9E%E5%85%AC%E5%AE%A4201_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E8%81%94%E5%92%8C%E6%9D%91.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -11936,9 +11936,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O96">
+      <c r="O96" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A4%A7%E9%B9%8F%E6%96%B0%E5%8C%BA%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E8%B7%AF84%E5%8F%B7_%E6%96%B0%E5%B1%8B%E5%9B%AD.html","查看证据(4项/7张)")</f>
-        <v/>
+        <v>查看证据(4项/7张)</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -12054,9 +12054,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O97">
+      <c r="O97" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B8%83%E6%96%B0%E8%B7%AF91_5_%E5%B8%83%E9%94%A6%E6%9D%91.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -12170,9 +12170,9 @@
           <t>2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O98">
+      <c r="O98" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B8%83%E6%96%B0%E8%B7%AF130%E5%8F%B7_%E5%8D%97%E5%9D%91%E5%9F%94.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -12287,9 +12287,9 @@
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O99">
+      <c r="O99" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E7%BB%9F%E5%BB%BA%E6%A5%BC_%E5%B8%83%E6%96%B0%E7%BB%9F%E5%BB%BA%E6%A5%BC.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -12404,9 +12404,9 @@
 1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-5)</t>
         </is>
       </c>
-      <c r="O100">
+      <c r="O100" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E7%A4%BE%E5%8C%BA%E6%B0%B4%E8%B4%9D%E6%9D%91_%E6%B0%B4%E8%B4%9D%E6%9D%91.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -12527,9 +12527,9 @@
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O101">
+      <c r="O101" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E5%8D%93%E8%B6%8A%E7%9A%87%E5%90%8E%E9%81%93_%E5%8D%93%E8%B6%8A%E7%9A%87%E5%90%8E%E9%81%93.html","查看证据(3项/6张)")</f>
-        <v/>
+        <v>查看证据(3项/6张)</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -12644,9 +12644,9 @@
 1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-4)</t>
         </is>
       </c>
-      <c r="O102">
+      <c r="O102" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E9%A3%9E%E5%A4%A7%E9%81%9310%E5%8F%B7_%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E4%BA%8C%E5%8C%BA.html","查看证据(2项/6张)")</f>
-        <v/>
+        <v>查看证据(2项/6张)</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
@@ -12763,9 +12763,9 @@
 5.3: 箱体不得标示与城管部门合作或监制等字样，不得标榜公益捐赠等信息。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O103">
+      <c r="O103" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E7%88%B1%E8%81%94%E7%A4%BE%E5%8C%BA%E7%88%B1%E5%8D%97%E8%B7%AF641%E5%8F%B7%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E8%8A%B1%E5%9B%AD_%E4%BA%94%E5%8C%BA_%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E4%BA%94%E5%8C%BA.html","查看证据(4项/6张)")</f>
-        <v/>
+        <v>查看证据(4项/6张)</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -12879,9 +12879,9 @@
           <t>4.1: 设备外观应使用“深i回收”标识，并公示服务单位、服务电话、回收品类、回收价格等基本信息，回收电话真实有效。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O104">
+      <c r="O104" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E7%88%B1%E5%8D%97%E8%B7%AF666%E5%8F%B7_%E6%98%9F%E6%B2%B3%E6%97%B6%E4%BB%A3%E8%8A%B1%E5%9B%AD.html","查看证据(1项/1张)")</f>
-        <v/>
+        <v>查看证据(1项/1张)</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -13002,9 +13002,9 @@
 1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O105">
+      <c r="O105" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%85%89%E7%8E%96%E6%82%A6%E5%8F%B0_%E9%BE%99%E5%85%89%E7%8E%96%E6%82%A6%E5%8F%B0.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -13125,9 +13125,9 @@
 1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O106">
+      <c r="O106" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%95%BF%E5%9F%8E%E9%87%8C%E7%A8%8B%E5%AE%B6%E5%9B%AD_%E9%95%BF%E5%9F%8E%E9%87%8C%E7%A8%8B%E5%AE%B6%E5%9B%AD.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -13242,9 +13242,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O107">
+      <c r="O107" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E8%BF%9C%E6%99%AF%E5%AE%B6%E5%9B%AD_%E8%BF%9C%E6%99%AF%E5%AE%B6%E5%9B%AD.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -13360,9 +13360,9 @@
 4.1: 设备外观应使用“深i回收”标识，并公示服务单位、服务电话、回收品类、回收价格等基本信息，回收电话真实有效。（1分） (-1)</t>
         </is>
       </c>
-      <c r="O108">
+      <c r="O108" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BB%84%E9%98%81%E8%B7%AF6%E5%8F%B7_%E5%9F%8E%E5%B8%82%E7%AB%8B%E6%96%B9%E8%8A%B1%E5%9B%AD_%E7%BB%BF%E6%99%AF%E5%A4%A7%E5%85%AC%E9%A6%86_.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -13477,9 +13477,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O109">
+      <c r="O109" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E6%B2%99%E5%9B%AD%E8%B7%AF%E4%B8%8E%E9%85%8D%E5%A5%97%E4%BA%8C%E8%B7%AF%E4%BA%A4%E5%8F%89%E8%B7%AF%E5%8F%A3%E5%BE%80%E4%B8%9C%E5%8D%97%E7%BA%A6100%E7%B1%B3_%E9%98%B3%E5%85%89%E5%A4%A9%E5%81%A5%E5%9F%8E%E4%B8%9C%E5%8D%97%E4%BE%A7%E7%BA%A650%E7%B1%B3_%E4%B8%AD%E6%A3%AE%E5%8F%8C%E5%AD%90%E5%BA%A7%E5%85%AC%E9%A6%86.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -13594,9 +13594,9 @@
 1.3: 各类收集容器的分类标志完整、正确、清晰。 （18分） (-3)</t>
         </is>
       </c>
-      <c r="O110">
+      <c r="O110" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%88%B1%E8%81%94%E7%A4%BE%E5%8C%BA%E5%89%8D%E8%BF%9B%E5%95%86%E4%B8%9A%E5%B9%BF%E5%9C%BA_%E5%8D%8E%E8%AE%B0%E5%86%9C%E5%AE%B6%E8%8F%9C.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -13710,9 +13710,9 @@
           <t>1.6: 各类收集容器的分类标志完整、正确、清晰。 (-6)</t>
         </is>
       </c>
-      <c r="O111">
+      <c r="O111" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E6%98%9F%E6%B2%B3%E6%97%B6%E4%BB%A3%E6%98%9F%E6%B2%B3COCO_Park_%E9%BE%99%E5%B2%97%E5%BA%97_%E9%BE%99%E5%B2%97%E6%98%9F%E6%B2%B3cocopark.html","查看证据(1项/7张)")</f>
-        <v/>
+        <v>查看证据(1项/7张)</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -13834,9 +13834,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O112">
+      <c r="O112" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD_%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD.html","查看证据(4项/5张)")</f>
-        <v/>
+        <v>查看证据(4项/5张)</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -13951,9 +13951,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O113">
+      <c r="O113" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%A4%A7%E5%8F%91%E5%9F%94%E7%A4%BE%E5%8C%BA%E5%88%9B%E5%85%B4%E6%97%B6%E4%BB%A3_%E5%88%9B%E5%85%B4%E6%97%B6%E4%BB%A3.html","查看证据(2项/2张)")</f>
-        <v/>
+        <v>查看证据(2项/2张)</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -14067,9 +14067,9 @@
           <t>1.6: 各类收集容器的分类标志完整、正确、清晰。 （9分） (-3)</t>
         </is>
       </c>
-      <c r="O114">
+      <c r="O114" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%A4%A7%E5%8F%91%E5%9F%94%E4%B8%9C%E6%9D%91%E4%B8%83%E5%B7%B711_12%E5%8F%B7%E4%B8%80_%E4%BA%8C%E6%A5%BC_%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E7%AC%AC%E4%BA%8C%E4%BA%BA%E6%B0%91%E5%8C%BB%E9%99%A2%E5%A4%A7%E5%8F%91%E5%9F%94%E7%A4%BE%E5%8C%BA%E5%81%A5%E5%BA%B7%E6%9C%8D%E5%8A%A1%E4%B8%AD%E5%BF%83.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -14185,9 +14185,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O115">
+      <c r="O115" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%90%89%E5%8D%8E%E8%B7%AF%E4%B8%8E%E4%BA%94%E5%92%8C%E5%A4%A7%E9%81%93%E4%BA%A4%E6%B1%87%E5%A4%84%E8%A5%BF%E5%8D%97%E8%A7%92_%E4%BD%B3%E5%8D%8E%E9%A2%86%E6%B1%87.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -14304,9 +14304,9 @@
 1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-5)</t>
         </is>
       </c>
-      <c r="O116">
+      <c r="O116" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA_%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA.html","查看证据(4项/10张)")</f>
-        <v/>
+        <v>查看证据(4项/10张)</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -14422,9 +14422,9 @@
 1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-5)</t>
         </is>
       </c>
-      <c r="O117">
+      <c r="O117" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E8%A5%BF%E6%B6%8C%E4%B8%89%E8%B7%AF_%E8%A5%BF%E8%BE%B9%E6%97%A7%E5%8C%BA.html","查看证据(3项/10张)")</f>
-        <v/>
+        <v>查看证据(3项/10张)</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -14539,9 +14539,9 @@
 1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O118">
+      <c r="O118" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%AE%9D%E5%AE%89%E5%9B%B4%E5%90%8E%E5%BA%95%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E5%90%8E%E5%BA%95%E5%B0%8F%E5%8C%BA.html","查看证据(2项/5张)")</f>
-        <v/>
+        <v>查看证据(2项/5张)</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -14655,9 +14655,9 @@
           <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分） (-3)</t>
         </is>
       </c>
-      <c r="O119">
+      <c r="O119" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E8%A5%BF%E6%B6%8C%E4%B8%89%E8%B7%AF50%E5%8F%B7%E4%BF%A1%E5%BE%B7_%E5%8D%A7%E9%BE%99%E5%9B%AD_%E8%8F%9C%E5%9B%AD%E5%B0%8F%E5%8C%BA.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -14778,9 +14778,9 @@
 1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O120">
+      <c r="O120" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E7%A5%A0%E5%A0%82%E5%8D%97%E5%8C%97%E5%8C%BA_%E7%A5%A0%E5%A0%82%E5%8D%97%E5%8C%97%E5%8C%BA.html","查看证据(3项/9张)")</f>
-        <v/>
+        <v>查看证据(3项/9张)</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -14895,9 +14895,9 @@
 1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分） (-3)</t>
         </is>
       </c>
-      <c r="O121">
+      <c r="O121" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%8C%AF%E5%85%B4%E8%B7%AF29%E5%8F%B7_%E5%B2%97%E7%93%A6%E5%9F%94%E5%B0%8F%E5%8C%BA.html","查看证据(2项/4张)")</f>
-        <v/>
+        <v>查看证据(2项/4张)</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -15012,9 +15012,9 @@
 1.15: 投放点均安装具备AI识别功能的视频监控设备，监控视野保持在合理角度。（4分） (-2)</t>
         </is>
       </c>
-      <c r="O122">
+      <c r="O122" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E5%9F%94%E5%A4%B4%E6%A1%A5%E5%B0%8F%E5%8C%BA_%E5%9F%94%E5%A4%B4%E6%A1%A5%E5%B0%8F%E5%8C%BA.html","查看证据(2项/5张)")</f>
-        <v/>
+        <v>查看证据(2项/5张)</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -15128,9 +15128,9 @@
           <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分） (-3)</t>
         </is>
       </c>
-      <c r="O123">
+      <c r="O123" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E5%A4%A7%E5%9B%AD%E6%A0%B9%E4%B8%80%E8%B7%AF_%E5%A4%A7%E5%9B%AD%E6%A0%B9.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -15247,9 +15247,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O124">
+      <c r="O124" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1062%E5%8F%B7_%E6%80%A1%E9%83%BD%E5%A4%A7%E5%8E%A6.html","查看证据(4项/5张)")</f>
-        <v/>
+        <v>查看证据(4项/5张)</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -15364,9 +15364,9 @@
 2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O125">
+      <c r="O125" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1066%E5%8F%B7_%E5%9B%BD%E6%97%85%E5%AE%BF%E8%88%8D.html","查看证据(2项/3张)")</f>
-        <v/>
+        <v>查看证据(2项/3张)</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -15487,9 +15487,9 @@
 4.4: 设备及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O126">
+      <c r="O126" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1021%E5%8F%B7_%E5%8F%8C%E5%9F%8E%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
@@ -15605,9 +15605,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O127">
+      <c r="O127" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1025%E5%8F%B7_%E6%B1%87%E6%B3%B0%E5%A4%A7%E5%8E%A6.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -15726,9 +15726,9 @@
           <t>1.6: 各类收集容器的分类标志完整、正确、清晰。 (-6)</t>
         </is>
       </c>
-      <c r="O128">
+      <c r="O128" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%90%89%E5%8D%8E%E8%B7%AF696%E5%8F%B7%E5%9D%82%E7%94%B0%E5%A4%A9%E8%99%B9%E5%95%86%E5%9C%BA_%E5%A4%A9%E8%99%B9%E6%95%B0%E7%A7%91%E5%95%86%E4%B8%9A%E8%82%A1%E4%BB%BD%E6%9C%89%E9%99%90%E5%85%AC%E5%8F%B8%E5%9D%82%E7%94%B0%E5%A4%A9%E8%99%B9%E5%95%86%E5%9C%BA.html","查看证据(1项/3张)")</f>
-        <v/>
+        <v>查看证据(1项/3张)</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -15846,9 +15846,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)</t>
         </is>
       </c>
-      <c r="O129">
+      <c r="O129" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%BE%99%E5%A1%98%E6%9D%91_%E9%BE%99%E5%A1%98%E6%9D%91.html","查看证据(5项/9张)")</f>
-        <v/>
+        <v>查看证据(5项/9张)</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -15968,9 +15968,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O130">
+      <c r="O130" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91%E6%B7%B1%E5%9C%B3%E9%BE%99%E8%B1%AA%E9%85%92%E5%BA%97_%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91.html","查看证据(7项/14张)")</f>
-        <v/>
+        <v>查看证据(7项/14张)</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -16086,9 +16086,9 @@
 1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
         </is>
       </c>
-      <c r="O131">
+      <c r="O131" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E6%B9%96%E5%BF%83%E5%A4%A7%E5%8E%A6_%E6%B9%96%E5%BF%83%E5%A4%A7%E5%8E%A6.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -16204,9 +16204,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O132">
+      <c r="O132" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%98%A5%E9%A3%8E%E8%B7%AF2001%E5%8F%B7_%E5%8D%97%E5%8D%8E%E8%A1%97%E5%B0%8F%E5%8C%BA.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -16320,9 +16320,9 @@
           <t>2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O133">
+      <c r="O133" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E6%B5%B7%E4%B8%B0%E8%8B%91_%E6%B5%B7%E4%B8%B0%E8%8B%91%E5%A4%A7%E5%8E%A6.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -16436,9 +16436,9 @@
           <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-4)</t>
         </is>
       </c>
-      <c r="O134">
+      <c r="O134" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B4%8B%E5%A4%A7%E5%8E%A6_%E5%8D%97%E6%B4%8B%E5%A4%A7%E5%8E%A6.html","查看证据(1项/2张)")</f>
-        <v/>
+        <v>查看证据(1项/2张)</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -16559,9 +16559,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O135">
+      <c r="O135" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%98%89%E5%BE%A1%E8%B1%AA%E5%9B%AD_%E5%98%89%E5%BE%A1%E8%B1%AA%E5%9B%AD.html","查看证据(3项/3张)")</f>
-        <v/>
+        <v>查看证据(3项/3张)</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -16677,9 +16677,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O136">
+      <c r="O136" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA_%E6%B3%B0%E5%B1%B1%E8%B7%AF_%E5%BE%A1%E7%8F%91%E8%B1%AA%E5%9B%AD.html","查看证据(3项/6张)")</f>
-        <v/>
+        <v>查看证据(3项/6张)</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
@@ -16798,9 +16798,9 @@
           <t>1.4: 各类收集容器的分类标志完整、正确、清晰。 (-6)</t>
         </is>
       </c>
-      <c r="O137">
+      <c r="O137" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E5%A4%A9%E5%81%A5%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6_%E5%A4%A9%E5%81%A5%E4%BA%91%E9%80%94%E5%88%9B%E6%99%BA%E4%B8%AD%E5%BF%83.html","查看证据(1项/4张)")</f>
-        <v/>
+        <v>查看证据(1项/4张)</v>
       </c>
       <c r="P137" t="inlineStr">
         <is>
@@ -16921,9 +16921,9 @@
 2.3: 各类垃圾及时清运。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O138">
+      <c r="O138" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8C%97%E7%8E%AF%E8%B7%AF%E4%B8%8E%E6%B7%B1%E4%BA%91%E8%B7%AF%E4%BA%A4%E7%95%8C%E5%A4%84_%E6%9C%97%E4%BE%A8%E5%B3%B0%E5%B1%85.html","查看证据(3项/8张)")</f>
-        <v/>
+        <v>查看证据(3项/8张)</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -17047,9 +17047,9 @@
 3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O139">
+      <c r="O139" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E6%B7%B1%E5%AE%89%E8%B7%AF33%E5%8F%B7%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C_%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C.html","查看证据(6项/11张)")</f>
-        <v/>
+        <v>查看证据(6项/11张)</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -17174,9 +17174,9 @@
 2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O140">
+      <c r="O140" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91_%E7%AE%80%E4%B8%8A%E6%9D%91.html","查看证据(7项/19张)")</f>
-        <v/>
+        <v>查看证据(7项/19张)</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -17297,9 +17297,9 @@
 2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
         </is>
       </c>
-      <c r="O141">
+      <c r="O141" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91%E4%B8%8A%E4%B8%B0%E8%8A%B1%E5%9B%AD_%E4%B8%8A%E4%B8%B0%E8%8A%B1%E5%9B%AD.html","查看证据(3项/4张)")</f>
-        <v/>
+        <v>查看证据(3项/4张)</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -17443,9 +17443,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（4处问题）</t>
         </is>
       </c>
-      <c r="G2">
+      <c r="G2" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91_%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="3">
@@ -17479,9 +17479,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）； （3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G3">
+      <c r="G3" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91_%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="4">
@@ -17515,9 +17515,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G4">
+      <c r="G4" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91_%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="5">
@@ -17551,9 +17551,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G5">
+      <c r="G5" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91_%E9%9A%94%E5%9C%B3%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="6">
@@ -17587,9 +17587,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G6">
+      <c r="G6" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E6%98%9F%E6%B2%B3%E4%BC%A0%E5%A5%87_%E6%98%9F%E6%B2%B3%E4%BC%A0%E5%A5%87.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="7">
@@ -17623,9 +17623,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G7">
+      <c r="G7" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E6%9D%BE%E4%BB%94%E5%9B%AD%E7%BB%B4%E4%B9%9F%E7%BA%B3%E9%85%92%E5%BA%97_%E9%BE%99%E5%8D%8E%E4%BA%BA%E6%B0%91%E5%8D%97%E8%B7%AF%E5%BA%97_%E6%B7%B1%E5%9C%B3%E5%B8%82%E6%82%A6%E7%BE%8E%E4%BD%B3%E9%85%92%E5%BA%97%E7%AE%A1%E7%90%86%E6%9C%89%E9%99%90%E5%85%AC%E5%8F%B8_%E7%BB%B4%E4%B9%9F%E7%BA%B3%E4%BA%BA%E6%B0%91%E5%8D%97%E8%B7%AF%E5%BA%97_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="8">
@@ -17659,9 +17659,9 @@
           <t>（2）主动向消费者提供客房一次性日用品(-10)（1处问题）</t>
         </is>
       </c>
-      <c r="G8">
+      <c r="G8" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E6%9D%BE%E4%BB%94%E5%9B%AD%E7%BB%B4%E4%B9%9F%E7%BA%B3%E9%85%92%E5%BA%97_%E9%BE%99%E5%8D%8E%E4%BA%BA%E6%B0%91%E5%8D%97%E8%B7%AF%E5%BA%97_%E6%B7%B1%E5%9C%B3%E5%B8%82%E6%82%A6%E7%BE%8E%E4%BD%B3%E9%85%92%E5%BA%97%E7%AE%A1%E7%90%86%E6%9C%89%E9%99%90%E5%85%AC%E5%8F%B8_%E7%BB%B4%E4%B9%9F%E7%BA%B3%E4%BA%BA%E6%B0%91%E5%8D%97%E8%B7%AF%E5%BA%97_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="9">
@@ -17695,9 +17695,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G9">
+      <c r="G9" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E8%8E%B1%E8%92%99_%E6%B0%B4%E6%A6%AD%E6%98%A5%E5%A4%A9_%E6%B0%B4%E6%A6%AD%E6%98%A5%E5%A4%A9%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="10">
@@ -17731,9 +17731,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（5处问题）</t>
         </is>
       </c>
-      <c r="G10">
+      <c r="G10" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E8%85%BE%E9%BE%99%E8%B7%AF124%E5%A4%A9%E8%99%B9%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83_%E9%BE%99%E5%8D%8E%E5%BA%97_%E4%B8%AD%E8%88%AA%E5%A4%A9%E9%80%B8%E7%AE%A1%E7%90%86%E5%A4%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="11">
@@ -17767,9 +17767,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G11">
+      <c r="G11" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E8%85%BE%E9%BE%99%E8%B7%AF124%E5%A4%A9%E8%99%B9%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83_%E9%BE%99%E5%8D%8E%E5%BA%97_%E4%B8%AD%E8%88%AA%E5%A4%A9%E9%80%B8%E7%AE%A1%E7%90%86%E5%A4%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="12">
@@ -17803,9 +17803,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G12">
+      <c r="G12" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E8%85%BE%E9%BE%99%E8%B7%AF124%E5%A4%A9%E8%99%B9%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83_%E9%BE%99%E5%8D%8E%E5%BA%97_%E4%B8%AD%E8%88%AA%E5%A4%A9%E9%80%B8%E7%AE%A1%E7%90%86%E5%A4%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="13">
@@ -17839,9 +17839,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（5处问题）</t>
         </is>
       </c>
-      <c r="G13">
+      <c r="G13" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E8%85%BE%E9%BE%99%E8%B7%AF124%E5%A4%A9%E8%99%B9%E8%B4%AD%E7%89%A9%E4%B8%AD%E5%BF%83_%E9%BE%99%E5%8D%8E%E5%BA%97_%E4%B8%AD%E8%88%AA%E5%A4%A9%E9%80%B8%E7%AE%A1%E7%90%86%E5%A4%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="14">
@@ -17875,9 +17875,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G14">
+      <c r="G14" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E4%B8%9C%E9%83%BD%E9%9B%85%E8%8B%91%E9%B9%8F%E5%8D%8E%E4%B8%96%E5%AE%B6%E5%8D%8E%E5%BA%9C_%E9%B9%8F%E5%8D%8E%E4%B8%96%E5%AE%B6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="15">
@@ -17911,9 +17911,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G15">
+      <c r="G15" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E7%89%B9%E5%8A%9B%E5%95%86%E5%8E%A6_%E7%89%B9%E5%8A%9B%E5%95%86%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="16">
@@ -17947,9 +17947,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G16">
+      <c r="G16" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%8E%E4%B8%9A%E5%A4%A7%E5%A4%8F_%E6%B7%B1%E5%8D%8E%E4%B8%9A%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="17">
@@ -17983,9 +17983,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G17">
+      <c r="G17" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%8E%E4%B8%9A%E5%A4%A7%E5%A4%8F_%E6%B7%B1%E5%8D%8E%E4%B8%9A%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="18">
@@ -18019,9 +18019,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G18">
+      <c r="G18" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E6%96%B0%E5%9B%AD%E8%B7%AF89%E5%8F%B7_%E4%B8%AD%E5%BF%83%E5%B9%BC%E5%84%BF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="19">
@@ -18055,9 +18055,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G19">
+      <c r="G19" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E7%9F%B3%E6%99%AF%E8%8A%B1%E5%9B%AD_%E5%BA%94%E4%BA%BA%E7%9F%B3%E7%9F%B3%E6%99%AF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="20">
@@ -18091,9 +18091,9 @@
           <t>（2）周边不干净整洁(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G20">
+      <c r="G20" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E7%9F%B3%E6%99%AF%E8%8A%B1%E5%9B%AD_%E5%BA%94%E4%BA%BA%E7%9F%B3%E7%9F%B3%E6%99%AF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="21">
@@ -18127,9 +18127,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G21">
+      <c r="G21" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E5%B9%B3%E6%B9%96%E8%8A%B1%E5%9B%AD_%E5%B9%B3%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="22">
@@ -18163,9 +18163,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G22">
+      <c r="G22" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E5%B9%B3%E6%B9%96%E8%8A%B1%E5%9B%AD_%E5%B9%B3%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="23">
@@ -18199,9 +18199,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G23">
+      <c r="G23" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E5%B9%B3%E6%B9%96%E8%8A%B1%E5%9B%AD_%E5%B9%B3%E6%B9%96%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="24">
@@ -18235,9 +18235,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G24">
+      <c r="G24" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="25">
@@ -18271,9 +18271,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G25">
+      <c r="G25" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="26">
@@ -18307,9 +18307,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
         </is>
       </c>
-      <c r="G26">
+      <c r="G26" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="27">
@@ -18343,9 +18343,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G27">
+      <c r="G27" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="28">
@@ -18379,9 +18379,9 @@
           <t>（2）柜门未保持关闭(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G28">
+      <c r="G28" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="29">
@@ -18415,9 +18415,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G29">
+      <c r="G29" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="30">
@@ -18451,9 +18451,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G30">
+      <c r="G30" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="31">
@@ -18487,9 +18487,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G31">
+      <c r="G31" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E7%A4%BE%E5%8C%BA%E5%A1%98%E5%A4%B4%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E8%83%8C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="32">
@@ -18523,9 +18523,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G32">
+      <c r="G32" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E9%94%A6%E5%86%A0%E5%8D%8E%E5%BA%AD_%E9%94%A6%E5%86%A0%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="33">
@@ -18559,9 +18559,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G33">
+      <c r="G33" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%B9%B3%E6%B9%96%E8%A1%97%E9%81%93%E9%94%A6%E5%86%A0%E5%8D%8E%E5%BA%AD_%E9%94%A6%E5%86%A0%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="34">
@@ -18595,9 +18595,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G34">
+      <c r="G34" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E5%8F%88%E4%B8%80%E6%9D%91_%E5%A1%98%E5%A4%B4%E5%8F%88%E4%B8%80%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="35">
@@ -18631,9 +18631,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G35">
+      <c r="G35" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E5%8F%88%E4%B8%80%E6%9D%91_%E5%A1%98%E5%A4%B4%E5%8F%88%E4%B8%80%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="36">
@@ -18667,9 +18667,9 @@
           <t>（2）周边不干净整洁(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G36">
+      <c r="G36" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E5%8F%88%E4%B8%80%E6%9D%91_%E5%A1%98%E5%A4%B4%E5%8F%88%E4%B8%80%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="37">
@@ -18703,9 +18703,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G37">
+      <c r="G37" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E8%A3%95%E5%92%8C%E5%8D%97%E8%A1%972_38%E5%8F%B7_%E8%8D%94%E5%9B%AD%E5%B8%82%E5%9C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="38">
@@ -18739,9 +18739,9 @@
           <t>（2）分类设施损坏或摆放不整齐，内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G38">
+      <c r="G38" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E8%A3%95%E5%92%8C%E5%8D%97%E8%A1%972_38%E5%8F%B7_%E8%8D%94%E5%9B%AD%E5%B8%82%E5%9C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="39">
@@ -18775,9 +18775,9 @@
           <t>（3）环境卫生不整洁（投放点有散落垃圾、杂物堆放，地面有明显污水污渍等）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G39">
+      <c r="G39" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E8%A3%95%E5%92%8C%E5%8D%97%E8%A1%972_38%E5%8F%B7_%E8%8D%94%E5%9B%AD%E5%B8%82%E5%9C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="40">
@@ -18811,9 +18811,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G40">
+      <c r="G40" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF7022%E5%8F%B7_%E9%B2%81%E7%8F%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="41">
@@ -18847,9 +18847,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G41">
+      <c r="G41" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF7022%E5%8F%B7_%E9%B2%81%E7%8F%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="42">
@@ -18883,9 +18883,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G42">
+      <c r="G42" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF7022%E5%8F%B7_%E9%B2%81%E7%8F%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="43">
@@ -18919,9 +18919,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G43">
+      <c r="G43" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF7024%E5%8F%B7_%E5%B8%82%E6%94%BF%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="44">
@@ -18955,9 +18955,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G44">
+      <c r="G44" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF7024%E5%8F%B7_%E5%B8%82%E6%94%BF%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="45">
@@ -18991,9 +18991,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G45">
+      <c r="G45" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF7024%E5%8F%B7_%E5%B8%82%E6%94%BF%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="46">
@@ -19027,9 +19027,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G46">
+      <c r="G46" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF77%E5%8F%B7_%E6%93%8E%E5%A4%A9%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="47">
@@ -19063,9 +19063,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G47">
+      <c r="G47" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF77%E5%8F%B7_%E6%93%8E%E5%A4%A9%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="48">
@@ -19099,9 +19099,9 @@
           <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G48">
+      <c r="G48" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF77%E5%8F%B7_%E6%93%8E%E5%A4%A9%E5%8D%8E%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="49">
@@ -19135,9 +19135,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G49">
+      <c r="G49" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%95%86%E6%8A%A5%E8%B7%AF18%E5%8F%B7_%E7%BF%A0%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="50">
@@ -19171,9 +19171,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G50">
+      <c r="G50" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%95%86%E6%8A%A5%E8%B7%AF18%E5%8F%B7_%E7%BF%A0%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="51">
@@ -19207,9 +19207,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G51">
+      <c r="G51" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%95%86%E6%8A%A5%E8%B7%AF18%E5%8F%B7_%E7%BF%A0%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="52">
@@ -19243,9 +19243,9 @@
           <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G52">
+      <c r="G52" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%95%86%E6%8A%A5%E8%B7%AF18%E5%8F%B7_%E7%BF%A0%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="53">
@@ -19279,9 +19279,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G53">
+      <c r="G53" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7_%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="54">
@@ -19315,9 +19315,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G54">
+      <c r="G54" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7_%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="55">
@@ -19351,9 +19351,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G55">
+      <c r="G55" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7_%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="56">
@@ -19387,9 +19387,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G56">
+      <c r="G56" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7_%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="57">
@@ -19423,9 +19423,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G57">
+      <c r="G57" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7_%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="58">
@@ -19459,9 +19459,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G58">
+      <c r="G58" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%95%BF%E5%B2%AD%E8%B7%AF13_2_%E9%95%BF%E5%B2%AD%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="59">
@@ -19495,9 +19495,9 @@
           <t>（2）收集容器缺失(-6)（1处问题）</t>
         </is>
       </c>
-      <c r="G59">
+      <c r="G59" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD%E4%B8%9C%E9%97%A8%E9%99%A2%E5%86%85101_%E5%8E%9F%E6%B1%81%E5%8E%9F%E5%91%B3%E9%A9%B4%E5%BA%84%E9%A4%90%E5%8E%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="60">
@@ -19531,9 +19531,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G60">
+      <c r="G60" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2031%E5%8F%B7%E6%83%A0%E5%90%8D%E8%8A%B1%E5%9B%AD%E4%B8%9C%E9%97%A8%E9%99%A2%E5%86%85101_%E5%8E%9F%E6%B1%81%E5%8E%9F%E5%91%B3%E9%A9%B4%E5%BA%84%E9%A4%90%E5%8E%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="61">
@@ -19567,9 +19567,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G61">
+      <c r="G61" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E8%8E%B2%E8%8A%B1%E8%B7%AF2069%E5%8F%B7_%E6%99%AF%E7%94%B0%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C180%E7%B1%B3_%E7%BC%94%E6%A2%A6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="62">
@@ -19603,9 +19603,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G62">
+      <c r="G62" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E8%8E%B2%E8%8A%B1%E8%B7%AF2069%E5%8F%B7_%E6%99%AF%E7%94%B0%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C180%E7%B1%B3_%E7%BC%94%E6%A2%A6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="63">
@@ -19639,9 +19639,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G63">
+      <c r="G63" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E8%8E%B2%E8%8A%B1%E8%B7%AF2069%E5%8F%B7_%E6%99%AF%E7%94%B0%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C180%E7%B1%B3_%E7%BC%94%E6%A2%A6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="64">
@@ -19675,9 +19675,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G64">
+      <c r="G64" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E8%8E%B2%E8%8A%B1%E8%B7%AF2069%E5%8F%B7_%E6%99%AF%E7%94%B0%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C180%E7%B1%B3_%E7%BC%94%E6%A2%A6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="65">
@@ -19711,9 +19711,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G65">
+      <c r="G65" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E8%8E%B2%E8%8A%B1%E8%B7%AF2069%E5%8F%B7_%E6%99%AF%E7%94%B0%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C180%E7%B1%B3_%E7%BC%94%E6%A2%A6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="66">
@@ -19747,9 +19747,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G66">
+      <c r="G66" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2008%E5%8F%B7_%E8%88%AA%E5%A4%A9%E6%99%B4%E5%B1%B1%E6%9C%88%E5%90%8D%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="67">
@@ -19783,9 +19783,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G67">
+      <c r="G67" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E7%BD%97%E6%B2%99%E8%B7%AF2008%E5%8F%B7_%E8%88%AA%E5%A4%A9%E6%99%B4%E5%B1%B1%E6%9C%88%E5%90%8D%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="68">
@@ -19819,9 +19819,9 @@
           <t>（2）柜门未保持关闭(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G68">
+      <c r="G68" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B2%99%E8%B7%AF2068%E5%8F%B7%E7%8E%89%E9%9B%85%E5%B1%85_%E7%8E%89%E9%9B%85%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="69">
@@ -19855,9 +19855,9 @@
           <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G69">
+      <c r="G69" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B2%99%E8%B7%AF2068%E5%8F%B7%E7%8E%89%E9%9B%85%E5%B1%85_%E7%8E%89%E9%9B%85%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="70">
@@ -19891,9 +19891,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G70">
+      <c r="G70" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E8%8E%B2%E5%A1%98%E8%A1%97%E9%81%93%E4%B8%83%E5%8F%B7%E8%B7%AF2%E5%8F%B7_%E5%85%AC%E4%BA%A4%E6%A2%A7%E6%A1%90%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="71">
@@ -19927,9 +19927,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G71">
+      <c r="G71" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E8%8E%B2%E5%A1%98%E8%A1%97%E9%81%93%E4%B8%83%E5%8F%B7%E8%B7%AF2%E5%8F%B7_%E5%85%AC%E4%BA%A4%E6%A2%A7%E6%A1%90%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="72">
@@ -19963,9 +19963,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G72">
+      <c r="G72" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E8%8E%B2%E5%A1%98%E8%A1%97%E9%81%93%E4%B8%83%E5%8F%B7%E8%B7%AF2%E5%8F%B7_%E5%85%AC%E4%BA%A4%E6%A2%A7%E6%A1%90%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="73">
@@ -19999,9 +19999,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G73">
+      <c r="G73" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E8%8E%B2%E5%A1%98%E8%A1%97%E9%81%93%E4%B8%83%E5%8F%B7%E8%B7%AF2%E5%8F%B7_%E5%85%AC%E4%BA%A4%E6%A2%A7%E6%A1%90%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="74">
@@ -20035,9 +20035,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G74">
+      <c r="G74" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E8%8E%B2%E5%A1%98%E8%A1%97%E9%81%93%E4%B8%83%E5%8F%B7%E8%B7%AF2%E5%8F%B7_%E5%85%AC%E4%BA%A4%E6%A2%A7%E6%A1%90%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="75">
@@ -20071,9 +20071,9 @@
           <t>（2）未在黄线划定区域内(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G75">
+      <c r="G75" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E8%8E%B2%E5%A1%98%E8%A1%97%E9%81%93%E4%B8%83%E5%8F%B7%E8%B7%AF2%E5%8F%B7_%E5%85%AC%E4%BA%A4%E6%A2%A7%E6%A1%90%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="76">
@@ -20107,9 +20107,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G76">
+      <c r="G76" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E8%8E%B2%E5%A1%98%E8%A1%97%E9%81%93%E4%B8%83%E5%8F%B7%E8%B7%AF2%E5%8F%B7_%E5%85%AC%E4%BA%A4%E6%A2%A7%E6%A1%90%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="77">
@@ -20143,9 +20143,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G77">
+      <c r="G77" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0366%E5%8F%B7_%E5%B1%B1%E6%B0%B4%E6%83%85%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="78">
@@ -20179,9 +20179,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G78">
+      <c r="G78" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0308%E5%8F%B7_%E5%A4%AA%E5%AD%90%E5%B1%B1%E5%BA%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="79">
@@ -20215,9 +20215,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G79">
+      <c r="G79" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0308%E5%8F%B7_%E5%A4%AA%E5%AD%90%E5%B1%B1%E5%BA%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="80">
@@ -20251,9 +20251,9 @@
           <t>（2）未成组摆放两分类收集容器(-3)</t>
         </is>
       </c>
-      <c r="G80">
+      <c r="G80" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%A5%BF%E8%B7%AF%E5%92%8C%E6%99%AF%E7%94%B0%E8%A5%BF%E4%BA%8C%E8%A1%97%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%A4%A9%E5%81%A5%E5%A4%A9%E9%AA%84%E5%85%AC%E4%BA%A4%E9%A6%96%E6%9C%AB%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="81">
@@ -20287,9 +20287,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G81">
+      <c r="G81" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%A5%BF%E8%B7%AF%E5%92%8C%E6%99%AF%E7%94%B0%E8%A5%BF%E4%BA%8C%E8%A1%97%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%A4%A9%E5%81%A5%E5%A4%A9%E9%AA%84%E5%85%AC%E4%BA%A4%E9%A6%96%E6%9C%AB%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="82">
@@ -20323,9 +20323,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G82">
+      <c r="G82" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0308%E5%8F%B7_%E5%B1%B1%E5%B1%85%E5%B2%81%E6%9C%88.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="83">
@@ -20359,9 +20359,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G83">
+      <c r="G83" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF83%E5%8F%B7_%E4%B8%87%E6%89%98%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="84">
@@ -20395,9 +20395,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G84">
+      <c r="G84" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF83%E5%8F%B7_%E4%B8%87%E6%89%98%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="85">
@@ -20431,9 +20431,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G85">
+      <c r="G85" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF83%E5%8F%B7_%E4%B8%87%E6%89%98%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="86">
@@ -20467,9 +20467,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G86">
+      <c r="G86" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF83%E5%8F%B7_%E4%B8%87%E6%89%98%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="87">
@@ -20503,9 +20503,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G87">
+      <c r="G87" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF81%E5%8F%B7_%E7%A2%A7%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="88">
@@ -20539,9 +20539,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G88">
+      <c r="G88" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF81%E5%8F%B7_%E7%A2%A7%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="89">
@@ -20575,9 +20575,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G89">
+      <c r="G89" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF81%E5%8F%B7_%E7%A2%A7%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="90">
@@ -20611,9 +20611,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G90">
+      <c r="G90" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF81%E5%8F%B7_%E7%A2%A7%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="91">
@@ -20647,9 +20647,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G91">
+      <c r="G91" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF81%E5%8F%B7_%E7%A2%A7%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="92">
@@ -20683,9 +20683,9 @@
           <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G92">
+      <c r="G92" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%99%AF%E7%94%B0%E8%B7%AF81%E5%8F%B7_%E7%A2%A7%E6%99%AF%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="93">
@@ -20719,9 +20719,9 @@
           <t>（3）240升及以下的生活垃圾收集容器未按要求套袋或套袋颜色错误(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G93">
+      <c r="G93" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C%E6%B7%B1%E5%9C%B3%E5%8D%97%E5%B1%B1%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C_%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="94">
@@ -20755,9 +20755,9 @@
           <t>（2）未将相关要求纳入日常巡查内容(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G94">
+      <c r="G94" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C%E6%B7%B1%E5%9C%B3%E5%8D%97%E5%B1%B1%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C_%E9%9D%92%E9%9D%92%E4%B8%96%E7%95%8C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="95">
@@ -20791,9 +20791,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
         </is>
       </c>
-      <c r="G95">
+      <c r="G95" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E4%B8%9C%E5%8C%BA_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E4%B8%9C%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="96">
@@ -20827,9 +20827,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）； （4）误时投放点未开放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G96">
+      <c r="G96" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E4%B8%9C%E5%8C%BA_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E4%B8%9C%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="97">
@@ -20863,9 +20863,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G97">
+      <c r="G97" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E4%B8%9C%E5%8C%BA_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E4%B8%9C%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="98">
@@ -20899,9 +20899,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G98">
+      <c r="G98" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E9%9D%92%E9%9D%92%E8%B7%AF2%E5%8F%B7_%E9%9D%92%E9%9D%92%E5%B1%B1%E5%BA%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="99">
@@ -20935,9 +20935,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G99">
+      <c r="G99" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E9%9D%92%E9%9D%92%E8%B7%AF2%E5%8F%B7_%E9%9D%92%E9%9D%92%E5%B1%B1%E5%BA%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="100">
@@ -20971,9 +20971,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G100">
+      <c r="G100" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E9%9D%92%E9%9D%92%E8%B7%AF2%E5%8F%B7_%E9%9D%92%E9%9D%92%E5%B1%B1%E5%BA%84.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="101">
@@ -21007,9 +21007,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G101">
+      <c r="G101" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E6%A8%9F%E9%98%81%E8%B7%AF329%E5%8F%B7_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="102">
@@ -21043,9 +21043,9 @@
           <t>（2）照明设施缺失、损坏或光线不足(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G102">
+      <c r="G102" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E6%A8%9F%E9%98%81%E8%B7%AF329%E5%8F%B7_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="103">
@@ -21079,9 +21079,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）； （3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G103">
+      <c r="G103" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E6%A8%9F%E9%98%81%E8%B7%AF329%E5%8F%B7_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="104">
@@ -21115,9 +21115,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G104">
+      <c r="G104" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E6%A8%9F%E9%98%81%E8%B7%AF329%E5%8F%B7_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="105">
@@ -21151,9 +21151,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G105">
+      <c r="G105" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E6%A8%9F%E9%98%81%E8%B7%AF329%E5%8F%B7_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="106">
@@ -21187,9 +21187,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（4处问题）</t>
         </is>
       </c>
-      <c r="G106">
+      <c r="G106" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E6%A8%9F%E9%98%81%E8%B7%AF329%E5%8F%B7_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="107">
@@ -21223,9 +21223,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G107">
+      <c r="G107" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA_%E6%A8%9F%E9%98%81%E8%B7%AF329%E5%8F%B7_%E7%AB%A0%E9%98%81%E8%80%81%E6%9D%91%E8%A5%BF%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="108">
@@ -21259,9 +21259,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）； （3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G108">
+      <c r="G108" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0369%E5%8F%B7_%E8%AF%BA%E5%BE%B7%E5%81%87%E6%97%A5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="109">
@@ -21295,9 +21295,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G109">
+      <c r="G109" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0369%E5%8F%B7_%E8%AF%BA%E5%BE%B7%E5%81%87%E6%97%A5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="110">
@@ -21331,9 +21331,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G110">
+      <c r="G110" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0369%E5%8F%B7_%E8%AF%BA%E5%BE%B7%E5%81%87%E6%97%A5%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="111">
@@ -21367,9 +21367,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G111">
+      <c r="G111" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0389%E5%8F%B7_%E9%9B%B7%E5%9C%B3%E7%A2%A7%E6%A6%95%E6%B9%BE%E6%B5%B7%E6%99%AF%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="112">
@@ -21403,9 +21403,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G112">
+      <c r="G112" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%B1%B1%E8%A1%97%E9%81%93%E5%89%8D%E6%B5%B7%E8%B7%AF0389%E5%8F%B7_%E9%9B%B7%E5%9C%B3%E7%A2%A7%E6%A6%95%E6%B9%BE%E6%B5%B7%E6%99%AF%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="113">
@@ -21439,9 +21439,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G113">
+      <c r="G113" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%80%81%E5%9D%91%E4%BA%95%E6%B0%B4%E9%BE%991%E5%8F%B7_%E4%BA%95%E6%B0%B4%E9%BE%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="114">
@@ -21475,9 +21475,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G114">
+      <c r="G114" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%80%81%E5%9D%91%E4%B8%9C%E5%9D%9183%E5%8F%B7_%E4%B8%9C%E5%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="115">
@@ -21511,9 +21511,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G115">
+      <c r="G115" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A1%98%E5%A4%B4%E5%A4%A7%E9%81%9368%E5%8F%B7_%E5%A1%98%E5%A4%B4%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="116">
@@ -21547,9 +21547,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G116">
+      <c r="G116" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A1%98%E5%A4%B4%E5%A4%A7%E9%81%9368%E5%8F%B7_%E5%A1%98%E5%A4%B4%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="117">
@@ -21583,9 +21583,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（2处问题）</t>
         </is>
       </c>
-      <c r="G117">
+      <c r="G117" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA%E5%A1%98%E5%A4%B4%E8%B7%AF12%E5%8F%B7%E6%97%81_%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="118">
@@ -21619,9 +21619,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G118">
+      <c r="G118" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA%E5%A1%98%E5%A4%B4%E8%B7%AF12%E5%8F%B7%E6%97%81_%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="119">
@@ -21655,9 +21655,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G119">
+      <c r="G119" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA%E5%A1%98%E5%A4%B4%E8%B7%AF12%E5%8F%B7%E6%97%81_%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="120">
@@ -21691,9 +21691,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G120">
+      <c r="G120" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E7%9F%B3%E5%B2%A9%E8%A1%97%E9%81%93%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA%E5%A1%98%E5%A4%B4%E8%B7%AF12%E5%8F%B7%E6%97%81_%E5%A1%98%E5%A4%B4%E4%B8%BD%E6%99%AF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="121">
@@ -21727,9 +21727,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G121">
+      <c r="G121" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B7%B1%E7%9B%90%E8%B7%AF1119%E5%8F%B7_%E6%B5%B7%E6%BB%A8%E5%81%87%E6%97%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="122">
@@ -21763,9 +21763,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G122">
+      <c r="G122" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B7%B1%E7%9B%90%E8%B7%AF1119%E5%8F%B7_%E6%B5%B7%E6%BB%A8%E5%81%87%E6%97%A5.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="123">
@@ -21799,9 +21799,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G123">
+      <c r="G123" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E6%B5%B7%E6%BB%A8%E5%81%87%E6%97%A5%E6%98%A5%E5%A4%A9%E6%B5%B7_%E6%98%A5%E5%A4%A9%E6%B5%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="124">
@@ -21835,9 +21835,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G124">
+      <c r="G124" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E6%98%9F%E6%B8%AF%E5%90%8D%E8%8B%91_%E6%98%9F%E6%B8%AF%E5%90%8D%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="125">
@@ -21871,9 +21871,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G125">
+      <c r="G125" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E5%8C%97%E5%B1%B1%E9%81%93127%E5%8F%B7_%E5%90%89%E9%BA%BB%E6%B9%96%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="126">
@@ -21907,9 +21907,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G126">
+      <c r="G126" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E5%92%8C%E4%BA%A8%E5%AE%B6%E5%AE%B6%E5%9B%AD_%E5%92%8C%E4%BA%A8%E9%9B%85%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="127">
@@ -21943,9 +21943,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G127">
+      <c r="G127" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E7%9B%90%E7%94%B0%E8%A1%97%E9%81%93%E5%92%8C%E4%BA%A8%E5%AE%B6%E5%AE%B6%E5%9B%AD_%E5%92%8C%E4%BA%A8%E9%9B%85%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="128">
@@ -21979,9 +21979,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G128">
+      <c r="G128" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%87%A4%E7%BF%94%E8%A1%9736%E5%8F%B7_%E6%B1%87%E9%94%A6%E5%90%8D%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="129">
@@ -22015,9 +22015,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G129">
+      <c r="G129" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%87%A4%E7%BF%94%E8%A1%9736%E5%8F%B7_%E6%B1%87%E9%94%A6%E5%90%8D%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="130">
@@ -22051,9 +22051,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G130">
+      <c r="G130" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1010%E5%8F%B7_%E9%94%A6%E7%BB%A3%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="131">
@@ -22087,9 +22087,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G131">
+      <c r="G131" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1010%E5%8F%B7_%E9%94%A6%E7%BB%A3%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="132">
@@ -22123,9 +22123,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G132">
+      <c r="G132" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1010%E5%8F%B7_%E9%94%A6%E7%BB%A3%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="133">
@@ -22159,9 +22159,9 @@
           <t>周边环境脏乱(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G133">
+      <c r="G133" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1010%E5%8F%B7_%E9%94%A6%E7%BB%A3%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="134">
@@ -22195,9 +22195,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G134">
+      <c r="G134" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1018%E5%8F%B7%E5%8C%97%E9%97%A8_%E6%B5%B7%E4%B8%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="135">
@@ -22231,9 +22231,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G135">
+      <c r="G135" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1018%E5%8F%B7%E5%8C%97%E9%97%A8_%E6%B5%B7%E4%B8%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="136">
@@ -22267,9 +22267,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G136">
+      <c r="G136" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1018%E5%8F%B7%E5%8C%97%E9%97%A8_%E6%B5%B7%E4%B8%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="137">
@@ -22303,9 +22303,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G137">
+      <c r="G137" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1018%E5%8F%B7%E5%8C%97%E9%97%A8_%E6%B5%B7%E4%B8%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="138">
@@ -22339,9 +22339,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）； （3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G138">
+      <c r="G138" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1018%E5%8F%B7%E5%8C%97%E9%97%A8_%E6%B5%B7%E4%B8%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="139">
@@ -22375,9 +22375,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G139">
+      <c r="G139" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%96%87%E9%94%A6%E4%B8%AD%E8%B7%AF1018%E5%8F%B7%E5%8C%97%E9%97%A8_%E6%B5%B7%E4%B8%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="140">
@@ -22411,9 +22411,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G140">
+      <c r="G140" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1002%E5%8F%B7_%E8%BD%BB%E5%B7%A5%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="141">
@@ -22447,9 +22447,9 @@
           <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G141">
+      <c r="G141" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1002%E5%8F%B7_%E8%BD%BB%E5%B7%A5%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="142">
@@ -22483,9 +22483,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G142">
+      <c r="G142" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1002%E5%8F%B7_%E8%BD%BB%E5%B7%A5%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="143">
@@ -22519,9 +22519,9 @@
           <t>（2）未使用(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G143">
+      <c r="G143" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1002%E5%8F%B7_%E8%BD%BB%E5%B7%A5%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="144">
@@ -22555,9 +22555,9 @@
           <t>（3）环境卫生不整洁（投放点有散落垃圾、杂物堆放，地面有明显污水污渍等）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G144">
+      <c r="G144" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E5%8C%97%E5%B1%B1%E5%A4%A7%E9%81%93%E5%B7%A5%E4%B8%9A%E5%8C%BA146%E5%8F%B7_%E5%8C%97%E5%B1%B1%E5%B7%A5%E4%B8%9A%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="145">
@@ -22591,9 +22591,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G145">
+      <c r="G145" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="146">
@@ -22627,9 +22627,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G146">
+      <c r="G146" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="147">
@@ -22663,9 +22663,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G147">
+      <c r="G147" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="148">
@@ -22699,9 +22699,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G148">
+      <c r="G148" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="149">
@@ -22735,9 +22735,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G149">
+      <c r="G149" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="150">
@@ -22771,9 +22771,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G150">
+      <c r="G150" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="151">
@@ -22807,9 +22807,9 @@
           <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G151">
+      <c r="G151" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="152">
@@ -22843,9 +22843,9 @@
           <t>（2）未使用(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G152">
+      <c r="G152" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%88%B1%E5%9B%BD%E8%B7%AF1040%E5%8F%B7%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2_%E5%8D%8E%E6%B7%B1%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="153">
@@ -22879,9 +22879,9 @@
           <t>（2）车辆挡住投放点过道、投放口前堆放大件杂物，阻碍居民投放(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G153">
+      <c r="G153" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1069%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E8%A5%BF%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="154">
@@ -22915,9 +22915,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G154">
+      <c r="G154" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1069%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E8%A5%BF%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="155">
@@ -22951,9 +22951,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G155">
+      <c r="G155" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1069%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E8%A5%BF%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="156">
@@ -22987,9 +22987,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G156">
+      <c r="G156" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1069%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E8%A5%BF%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="157">
@@ -23023,9 +23023,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G157">
+      <c r="G157" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1069%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E8%A5%BF%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="158">
@@ -23059,9 +23059,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G158">
+      <c r="G158" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="159">
@@ -23095,9 +23095,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）； （3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G159">
+      <c r="G159" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="160">
@@ -23131,9 +23131,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G160">
+      <c r="G160" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="161">
@@ -23167,9 +23167,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G161">
+      <c r="G161" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="162">
@@ -23203,9 +23203,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G162">
+      <c r="G162" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="163">
@@ -23239,9 +23239,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G163">
+      <c r="G163" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="164">
@@ -23275,9 +23275,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（3处问题）</t>
         </is>
       </c>
-      <c r="G164">
+      <c r="G164" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="165">
@@ -23311,9 +23311,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G165">
+      <c r="G165" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="166">
@@ -23347,9 +23347,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G166">
+      <c r="G166" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E7%BA%A2%E8%8A%B1%E4%B8%AD%E8%B7%AF_25%E5%B0%8F%E5%8C%BA%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="167">
@@ -23383,9 +23383,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G167">
+      <c r="G167" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%8E%E4%B8%BD%E8%B7%AF1067%E5%8F%B7_%E9%87%91%E7%9B%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="168">
@@ -23419,9 +23419,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G168">
+      <c r="G168" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%8E%E4%B8%BD%E8%B7%AF1067%E5%8F%B7_%E9%87%91%E7%9B%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="169">
@@ -23455,9 +23455,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G169">
+      <c r="G169" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%8E%E4%B8%BD%E8%B7%AF1067%E5%8F%B7_%E9%87%91%E7%9B%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="170">
@@ -23491,9 +23491,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G170">
+      <c r="G170" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%8E%E4%B8%BD%E8%B7%AF1067%E5%8F%B7_%E9%87%91%E7%9B%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="171">
@@ -23527,9 +23527,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G171">
+      <c r="G171" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%8E%E4%B8%BD%E8%B7%AF1067%E5%8F%B7_%E9%87%91%E7%9B%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="172">
@@ -23563,9 +23563,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G172">
+      <c r="G172" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%8E%E4%B8%BD%E8%B7%AF1067%E5%8F%B7_%E9%87%91%E7%9B%BE%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="173">
@@ -23599,9 +23599,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G173">
+      <c r="G173" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1049%E5%8F%B7%E9%99%84%E8%BF%91_1049%E5%8F%B7%E4%B8%AD%E8%A1%8C%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="174">
@@ -23635,9 +23635,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G174">
+      <c r="G174" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%8E%E4%B8%BD%E8%B7%AF1049%E5%8F%B7%E9%99%84%E8%BF%91_1049%E5%8F%B7%E4%B8%AD%E8%A1%8C%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="175">
@@ -23671,9 +23671,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G175">
+      <c r="G175" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1031%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="176">
@@ -23707,9 +23707,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G176">
+      <c r="G176" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1031%E5%8F%B7_%E5%8D%8E%E4%B8%BD%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="177">
@@ -23743,9 +23743,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G177">
+      <c r="G177" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1011%E5%8F%B7_%E5%8F%8B%E8%B0%8A%E5%85%AC%E5%8F%B8%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="178">
@@ -23779,9 +23779,9 @@
           <t>（2）照明设施缺失、损坏或光线不足(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G178">
+      <c r="G178" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1011%E5%8F%B7_%E5%8F%8B%E8%B0%8A%E5%85%AC%E5%8F%B8%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="179">
@@ -23815,9 +23815,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G179">
+      <c r="G179" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1011%E5%8F%B7_%E5%8F%8B%E8%B0%8A%E5%85%AC%E5%8F%B8%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="180">
@@ -23851,9 +23851,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G180">
+      <c r="G180" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1011%E5%8F%B7_%E5%8F%8B%E8%B0%8A%E5%85%AC%E5%8F%B8%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="181">
@@ -23887,9 +23887,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G181">
+      <c r="G181" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%8D%8E%E4%B8%BD%E8%B7%AF1011%E5%8F%B7_%E5%8F%8B%E8%B0%8A%E5%85%AC%E5%8F%B8%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="182">
@@ -23923,9 +23923,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G182">
+      <c r="G182" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%87%A4%E5%87%B0%E8%B7%AF166%E5%8F%B7_%E5%87%A4%E5%87%B0%E8%B7%AF166%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="183">
@@ -23959,9 +23959,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G183">
+      <c r="G183" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%87%A4%E5%87%B0%E8%B7%AF166%E5%8F%B7_%E5%87%A4%E5%87%B0%E8%B7%AF166%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="184">
@@ -23995,9 +23995,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G184">
+      <c r="G184" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E9%BB%84%E8%B4%9D%E8%A1%97%E9%81%93%E5%87%A4%E5%87%B0%E8%B7%AF166%E5%8F%B7_%E5%87%A4%E5%87%B0%E8%B7%AF166%E5%8F%B7%E5%A4%A7%E9%99%A2.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="185">
@@ -24031,9 +24031,9 @@
           <t>（2）收集容器缺失(-6)（1处问题）</t>
         </is>
       </c>
-      <c r="G185">
+      <c r="G185" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E6%8C%AF%E6%98%8E%E8%B7%AF161%E5%8F%B7%E5%9B%9B%E5%AD%A3%E6%98%9F%E5%9F%8E_%E7%B2%A4%E6%B5%B7%E6%B8%94%E6%B8%AF.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="186">
@@ -24067,9 +24067,9 @@
           <t>（2）未设置光盘行动、节约粮食等宣传海报或温馨提示等(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G186">
+      <c r="G186" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E6%8C%AF%E6%98%8E%E8%B7%AF161%E5%8F%B7%E5%9B%9B%E5%AD%A3%E6%98%9F%E5%9F%8E_%E7%B2%A4%E6%B5%B7%E6%B8%94%E6%B8%AF.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="187">
@@ -24103,9 +24103,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G187">
+      <c r="G187" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%BA%B7%E4%B9%90%E8%B7%AF%E5%85%AC%E6%98%8E%E8%A1%97%E5%BF%83%E5%85%AC%E5%9B%AD_%E5%8D%97%E5%9B%9B%E5%B7%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="188">
@@ -24139,9 +24139,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G188">
+      <c r="G188" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%BA%B7%E4%B9%90%E8%B7%AF%E5%85%AC%E6%98%8E%E8%A1%97%E5%BF%83%E5%85%AC%E5%9B%AD_%E5%8D%97%E5%9B%9B%E5%B7%B7.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="189">
@@ -24175,9 +24175,9 @@
           <t>（2）分类设施损坏或摆放不整齐，内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-3)（1处问题）； （4）其他问题说明（备注描述） (-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G189">
+      <c r="G189" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E9%93%81%E7%94%B2%E7%A7%91%E6%8A%80%E5%9B%AD_%E9%93%81%E7%94%B2%E5%B7%A5%E4%B8%9A%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="190">
@@ -24211,9 +24211,9 @@
           <t>（2）容器存在明显陈旧性脏污(-2)</t>
         </is>
       </c>
-      <c r="G190">
+      <c r="G190" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E9%93%81%E7%94%B2%E7%A7%91%E6%8A%80%E5%9B%AD_%E9%93%81%E7%94%B2%E5%B7%A5%E4%B8%9A%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="191">
@@ -24247,9 +24247,9 @@
           <t>（2）将工业固体废物混入生活垃圾收运体系(-6)（1处问题）</t>
         </is>
       </c>
-      <c r="G191">
+      <c r="G191" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E9%93%81%E7%94%B2%E7%A7%91%E6%8A%80%E5%9B%AD_%E9%93%81%E7%94%B2%E5%B7%A5%E4%B8%9A%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="192">
@@ -24283,9 +24283,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G192">
+      <c r="G192" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%85%AC%E6%98%8E%E8%A7%A3%E6%94%BE%E8%A1%97%E6%B5%B7%E4%BF%A1%E8%8A%B1%E5%9B%AD_%E5%AF%8C%E5%88%A9%E8%B7%AF_%E6%97%A7%E8%A1%97%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="193">
@@ -24319,9 +24319,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G193">
+      <c r="G193" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%85%AC%E6%98%8E%E8%A7%A3%E6%94%BE%E8%A1%97%E6%B5%B7%E4%BF%A1%E8%8A%B1%E5%9B%AD_%E5%AF%8C%E5%88%A9%E8%B7%AF_%E6%97%A7%E8%A1%97%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="194">
@@ -24355,9 +24355,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）； （3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G194">
+      <c r="G194" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%85%AC%E6%98%8E%E8%A7%A3%E6%94%BE%E8%A1%97%E6%B5%B7%E4%BF%A1%E8%8A%B1%E5%9B%AD_%E5%AF%8C%E5%88%A9%E8%B7%AF_%E6%97%A7%E8%A1%97%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="195">
@@ -24391,9 +24391,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G195">
+      <c r="G195" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%85%AC%E6%98%8E%E8%A7%A3%E6%94%BE%E8%A1%97%E6%B5%B7%E4%BF%A1%E8%8A%B1%E5%9B%AD_%E5%AF%8C%E5%88%A9%E8%B7%AF_%E6%97%A7%E8%A1%97%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="196">
@@ -24427,9 +24427,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G196">
+      <c r="G196" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%85%AC%E6%98%8E%E8%A7%A3%E6%94%BE%E8%A1%97%E6%B5%B7%E4%BF%A1%E8%8A%B1%E5%9B%AD_%E5%AF%8C%E5%88%A9%E8%B7%AF_%E6%97%A7%E8%A1%97%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="197">
@@ -24463,9 +24463,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G197">
+      <c r="G197" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%85%AC%E6%98%8E%E8%A7%A3%E6%94%BE%E8%A1%97%E6%B5%B7%E4%BF%A1%E8%8A%B1%E5%9B%AD_%E5%AF%8C%E5%88%A9%E8%B7%AF_%E6%97%A7%E8%A1%97%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="198">
@@ -24499,9 +24499,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G198">
+      <c r="G198" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%85%89%E6%98%8E%E5%8C%BA%E5%85%AC%E6%98%8E%E8%A1%97%E9%81%93%E5%85%AC%E6%98%8E%E8%A7%A3%E6%94%BE%E8%A1%97%E6%B5%B7%E4%BF%A1%E8%8A%B1%E5%9B%AD_%E5%AF%8C%E5%88%A9%E8%B7%AF_%E6%97%A7%E8%A1%97%E7%89%87%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="199">
@@ -24535,9 +24535,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G199">
+      <c r="G199" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2069%E5%8F%B7_%E9%AA%8F%E7%9A%87%E5%90%8D%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="200">
@@ -24571,9 +24571,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G200">
+      <c r="G200" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2069%E5%8F%B7_%E9%AA%8F%E7%9A%87%E5%90%8D%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="201">
@@ -24607,9 +24607,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G201">
+      <c r="G201" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2069%E5%8F%B7_%E9%AA%8F%E7%9A%87%E5%90%8D%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="202">
@@ -24643,9 +24643,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G202">
+      <c r="G202" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2069%E5%8F%B7_%E9%AA%8F%E7%9A%87%E5%90%8D%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="203">
@@ -24679,9 +24679,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G203">
+      <c r="G203" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2069%E5%8F%B7_%E9%AA%8F%E7%9A%87%E5%90%8D%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="204">
@@ -24715,9 +24715,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G204">
+      <c r="G204" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2069%E5%8F%B7_%E9%AA%8F%E7%9A%87%E5%90%8D%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="205">
@@ -24751,9 +24751,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G205">
+      <c r="G205" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2053%E5%8F%B7%E9%93%B6%E6%B3%B0%E8%8B%91_%E9%93%B6%E6%B3%B0%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="206">
@@ -24787,9 +24787,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G206">
+      <c r="G206" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2053%E5%8F%B7%E9%93%B6%E6%B3%B0%E8%8B%91_%E9%93%B6%E6%B3%B0%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="207">
@@ -24823,9 +24823,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G207">
+      <c r="G207" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2053%E5%8F%B7%E9%93%B6%E6%B3%B0%E8%8B%91_%E9%93%B6%E6%B3%B0%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="208">
@@ -24859,9 +24859,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G208">
+      <c r="G208" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2053%E5%8F%B7%E9%93%B6%E6%B3%B0%E8%8B%91_%E9%93%B6%E6%B3%B0%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="209">
@@ -24895,9 +24895,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G209">
+      <c r="G209" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E5%BC%BA%E8%B7%AF2053%E5%8F%B7%E9%93%B6%E6%B3%B0%E8%8B%91_%E9%93%B6%E6%B3%B0%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="210">
@@ -24931,9 +24931,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G210">
+      <c r="G210" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%8F%A9%E6%8F%90%E8%B7%AF48%E5%8F%B7_%E5%8D%97%E5%85%89%E5%90%8D%E4%BB%95%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="211">
@@ -24967,9 +24967,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）； （3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G211">
+      <c r="G211" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%8F%A9%E6%8F%90%E8%B7%AF48%E5%8F%B7_%E5%8D%97%E5%85%89%E5%90%8D%E4%BB%95%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="212">
@@ -25003,9 +25003,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G212">
+      <c r="G212" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%8F%A9%E6%8F%90%E8%B7%AF48%E5%8F%B7_%E5%8D%97%E5%85%89%E5%90%8D%E4%BB%95%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="213">
@@ -25039,9 +25039,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G213">
+      <c r="G213" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%8F%A9%E6%8F%90%E8%B7%AF48%E5%8F%B7_%E5%8D%97%E5%85%89%E5%90%8D%E4%BB%95%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="214">
@@ -25075,9 +25075,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G214">
+      <c r="G214" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%8F%A9%E6%8F%90%E8%B7%AF48%E5%8F%B7_%E5%8D%97%E5%85%89%E5%90%8D%E4%BB%95%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="215">
@@ -25111,9 +25111,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G215">
+      <c r="G215" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%8F%A9%E6%8F%90%E8%B7%AF48%E5%8F%B7_%E5%8D%97%E5%85%89%E5%90%8D%E4%BB%95%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="216">
@@ -25147,9 +25147,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）； （3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G216">
+      <c r="G216" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E4%BF%9D%E7%A8%8E%E5%8C%BA%E8%8F%A9%E6%8F%90%E8%B7%AF18%E5%8F%B7%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD_%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="217">
@@ -25183,9 +25183,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G217">
+      <c r="G217" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E4%BF%9D%E7%A8%8E%E5%8C%BA%E8%8F%A9%E6%8F%90%E8%B7%AF18%E5%8F%B7%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD_%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="218">
@@ -25219,9 +25219,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G218">
+      <c r="G218" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E4%BF%9D%E7%A8%8E%E5%8C%BA%E8%8F%A9%E6%8F%90%E8%B7%AF18%E5%8F%B7%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD_%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="219">
@@ -25255,9 +25255,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G219">
+      <c r="G219" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E4%BF%9D%E7%A8%8E%E5%8C%BA%E8%8F%A9%E6%8F%90%E8%B7%AF18%E5%8F%B7%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD_%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="220">
@@ -25291,9 +25291,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G220">
+      <c r="G220" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E4%BF%9D%E7%A8%8E%E5%8C%BA%E8%8F%A9%E6%8F%90%E8%B7%AF18%E5%8F%B7%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD_%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="221">
@@ -25327,9 +25327,9 @@
           <t>周边环境脏乱(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G221">
+      <c r="G221" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E4%BF%9D%E7%A8%8E%E5%8C%BA%E8%8F%A9%E6%8F%90%E8%B7%AF18%E5%8F%B7%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD_%E5%98%89%E7%A6%8F%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="222">
@@ -25363,9 +25363,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G222">
+      <c r="G222" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%A4%B4%E8%A1%97%E9%81%93%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%A6%96%E5%9F%8E_%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="223">
@@ -25399,9 +25399,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G223">
+      <c r="G223" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%A4%B4%E8%A1%97%E9%81%93%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%A6%96%E5%9F%8E_%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="224">
@@ -25435,9 +25435,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G224">
+      <c r="G224" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%A4%B4%E8%A1%97%E9%81%93%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%A6%96%E5%9F%8E_%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="225">
@@ -25471,9 +25471,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G225">
+      <c r="G225" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%A4%B4%E8%A1%97%E9%81%93%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%A6%96%E5%9F%8E_%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="226">
@@ -25507,9 +25507,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G226">
+      <c r="G226" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%8D%97%E5%A4%B4%E8%A1%97%E9%81%93%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD%E9%A6%96%E5%9F%8E_%E9%B8%BF%E6%B4%B2%E6%96%B0%E9%83%BD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="227">
@@ -25543,9 +25543,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G227">
+      <c r="G227" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0_%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="228">
@@ -25579,9 +25579,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G228">
+      <c r="G228" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0_%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="229">
@@ -25615,9 +25615,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G229">
+      <c r="G229" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0_%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="230">
@@ -25651,9 +25651,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G230">
+      <c r="G230" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0_%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="231">
@@ -25687,9 +25687,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）； （5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G231">
+      <c r="G231" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0_%E5%98%89%E5%8D%97%E7%BE%8E%E5%9C%B0.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="232">
@@ -25723,9 +25723,9 @@
           <t>（2）收集容器缺失(5)（1处问题）</t>
         </is>
       </c>
-      <c r="G232">
+      <c r="G232" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%AF%94%E5%AE%9D%E4%BA%8C%E8%B7%AF83%E5%8F%B7_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E5%B7%A5%E4%BD%9C%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="233">
@@ -25759,9 +25759,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G233">
+      <c r="G233" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA_%E7%BA%A2%E8%8A%B1%E8%B7%AF136%E5%8F%B7_%E5%8D%97%E5%B1%B1%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="234">
@@ -25795,9 +25795,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G234">
+      <c r="G234" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA_%E7%BA%A2%E8%8A%B1%E8%B7%AF136%E5%8F%B7_%E5%8D%97%E5%B1%B1%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="235">
@@ -25831,9 +25831,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G235">
+      <c r="G235" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA_%E7%BA%A2%E8%8A%B1%E8%B7%AF136%E5%8F%B7_%E5%8D%97%E5%B1%B1%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="236">
@@ -25867,9 +25867,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G236">
+      <c r="G236" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA_%E7%BA%A2%E8%8A%B1%E8%B7%AF136%E5%8F%B7_%E5%8D%97%E5%B1%B1%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="237">
@@ -25903,9 +25903,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G237">
+      <c r="G237" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA_%E7%BA%A2%E8%8A%B1%E8%B7%AF136%E5%8F%B7_%E5%8D%97%E5%B1%B1%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="238">
@@ -25939,9 +25939,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G238">
+      <c r="G238" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA_%E7%BA%A2%E8%8A%B1%E8%B7%AF136%E5%8F%B7_%E5%8D%97%E5%B1%B1%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="239">
@@ -25975,9 +25975,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （4）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G239">
+      <c r="G239" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA_%E7%BA%A2%E8%8A%B1%E8%B7%AF136%E5%8F%B7_%E5%8D%97%E5%B1%B1%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="240">
@@ -26011,9 +26011,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G240">
+      <c r="G240" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E6%B0%B4%E4%B8%80%E6%9D%9111%E5%8F%B7_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E6%B0%B4%E4%B8%80%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="241">
@@ -26047,9 +26047,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G241">
+      <c r="G241" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E6%B0%B4%E4%BA%8C%E6%9D%9113_4%E5%8F%B7_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E6%B0%B4%E4%BA%8C%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="242">
@@ -26083,9 +26083,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G242">
+      <c r="G242" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91_%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="243">
@@ -26119,9 +26119,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G243">
+      <c r="G243" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91_%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="244">
@@ -26155,9 +26155,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G244">
+      <c r="G244" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91_%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="245">
@@ -26191,9 +26191,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-4)（1处问题）</t>
         </is>
       </c>
-      <c r="G245">
+      <c r="G245" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91_%E4%B8%80%E7%94%B2%E6%B5%B7%E8%BE%B9%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="246">
@@ -26227,9 +26227,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G246">
+      <c r="G246" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E5%8D%8E%E4%B8%89%E8%B7%AF8%E5%8F%B7_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C290%E7%B1%B3_%E6%81%92%E8%BF%90%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="247">
@@ -26263,9 +26263,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G247">
+      <c r="G247" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E5%8D%8E%E4%B8%89%E8%B7%AF8%E5%8F%B7_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C290%E7%B1%B3_%E6%81%92%E8%BF%90%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="248">
@@ -26299,9 +26299,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G248">
+      <c r="G248" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E5%8D%8E%E4%B8%89%E8%B7%AF8%E5%8F%B7_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C290%E7%B1%B3_%E6%81%92%E8%BF%90%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="249">
@@ -26335,9 +26335,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G249">
+      <c r="G249" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E5%8D%8E%E4%B8%89%E8%B7%AF8%E5%8F%B7_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C290%E7%B1%B3_%E6%81%92%E8%BF%90%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="250">
@@ -26371,9 +26371,9 @@
           <t>（4）其他问题说明（备注描述）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G250">
+      <c r="G250" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E7%A6%8F%E5%8D%8E3%E8%B7%AF_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C370%E7%B1%B3_%E9%87%91%E7%94%B0%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="251">
@@ -26407,9 +26407,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G251">
+      <c r="G251" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E7%A6%8F%E5%8D%8E3%E8%B7%AF_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C370%E7%B1%B3_%E9%87%91%E7%94%B0%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="252">
@@ -26443,9 +26443,9 @@
           <t>（2）投放口被封闭或遮挡(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G252">
+      <c r="G252" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E7%A6%8F%E5%8D%8E3%E8%B7%AF_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C370%E7%B1%B3_%E9%87%91%E7%94%B0%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="253">
@@ -26479,9 +26479,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G253">
+      <c r="G253" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E7%A6%8F%E5%8D%8E3%E8%B7%AF_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99D%E5%8F%A3%E6%AD%A5%E8%A1%8C370%E7%B1%B3_%E9%87%91%E7%94%B0%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="254">
@@ -26515,9 +26515,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G254">
+      <c r="G254" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%BD%A9%E7%94%B0%E8%B7%AF%E5%92%8C%E7%A6%8F%E5%8D%8E%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%BD%A9%E7%A6%8F%E5%A4%A7%E5%8E%A6%E9%99%84%E8%BF%91_%E5%B2%97%E5%8E%A6%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="255">
@@ -26551,9 +26551,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G255">
+      <c r="G255" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%BD%A9%E7%94%B0%E8%B7%AF%E5%92%8C%E7%A6%8F%E5%8D%8E%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%BD%A9%E7%A6%8F%E5%A4%A7%E5%8E%A6%E9%99%84%E8%BF%91_%E5%B2%97%E5%8E%A6%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="256">
@@ -26587,9 +26587,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）； （4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G256">
+      <c r="G256" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%BD%A9%E7%94%B0%E8%B7%AF%E5%92%8C%E7%A6%8F%E5%8D%8E%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%BD%A9%E7%A6%8F%E5%A4%A7%E5%8E%A6%E9%99%84%E8%BF%91_%E5%B2%97%E5%8E%A6%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="257">
@@ -26623,9 +26623,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G257">
+      <c r="G257" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%BD%A9%E7%94%B0%E8%B7%AF%E5%92%8C%E7%A6%8F%E5%8D%8E%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%BD%A9%E7%A6%8F%E5%A4%A7%E5%8E%A6%E9%99%84%E8%BF%91_%E5%B2%97%E5%8E%A6%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="258">
@@ -26659,9 +26659,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G258">
+      <c r="G258" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%BD%A9%E7%94%B0%E8%B7%AF%E5%92%8C%E7%A6%8F%E5%8D%8E%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%BD%A9%E7%A6%8F%E5%A4%A7%E5%8E%A6%E9%99%84%E8%BF%91_%E5%B2%97%E5%8E%A6%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="259">
@@ -26695,9 +26695,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G259">
+      <c r="G259" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%BD%A9%E7%94%B0%E8%B7%AF%E5%92%8C%E7%A6%8F%E5%8D%8E%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%BD%A9%E7%A6%8F%E5%A4%A7%E5%8E%A6%E9%99%84%E8%BF%91_%E5%B2%97%E5%8E%A6%E5%9F%8E.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="260">
@@ -26731,9 +26731,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G260">
+      <c r="G260" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%B2%97%E5%8E%A6%E7%A4%BE%E5%8C%BA%E6%98%9F%E6%B2%B3%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6_%E6%98%9F%E6%B2%B3%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="261">
@@ -26767,9 +26767,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G261">
+      <c r="G261" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%B2%97%E5%8E%A6%E7%A4%BE%E5%8C%BA%E6%98%9F%E6%B2%B3%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6_%E6%98%9F%E6%B2%B3%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="262">
@@ -26803,9 +26803,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G262">
+      <c r="G262" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E5%B2%97%E5%8E%A6%E7%A4%BE%E5%8C%BA%E6%98%9F%E6%B2%B3%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6_%E6%98%9F%E6%B2%B3%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="263">
@@ -26839,9 +26839,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G263">
+      <c r="G263" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%93%E4%B8%8E%E9%87%91%E7%94%B0%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E6%B7%B1%E5%9C%B3%E4%B8%AD%E5%BF%83%E5%A4%A9%E5%85%83%E5%85%AC%E5%AF%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="264">
@@ -26875,9 +26875,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G264">
+      <c r="G264" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%93%E4%B8%8E%E9%87%91%E7%94%B0%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E6%B7%B1%E5%9C%B3%E4%B8%AD%E5%BF%83%E5%A4%A9%E5%85%83%E5%85%AC%E5%AF%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="265">
@@ -26911,9 +26911,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G265">
+      <c r="G265" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%93%E4%B8%8E%E9%87%91%E7%94%B0%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E6%B7%B1%E5%9C%B3%E4%B8%AD%E5%BF%83%E5%A4%A9%E5%85%83%E5%85%AC%E5%AF%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="266">
@@ -26947,9 +26947,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G266">
+      <c r="G266" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%93%E4%B8%8E%E9%87%91%E7%94%B0%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E6%B7%B1%E5%9C%B3%E4%B8%AD%E5%BF%83%E5%A4%A9%E5%85%83%E5%85%AC%E5%AF%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="267">
@@ -26983,9 +26983,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G267">
+      <c r="G267" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%93%E4%B8%8E%E9%87%91%E7%94%B0%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E6%B7%B1%E5%9C%B3%E4%B8%AD%E5%BF%83%E5%A4%A9%E5%85%83%E5%85%AC%E5%AF%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="268">
@@ -27019,9 +27019,9 @@
           <t>（2）围挡设置不规范（未设置围挡，围挡封闭不全，或使用移动式栅栏、水马等围合）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G268">
+      <c r="G268" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%A6%8F%E7%94%B0%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%93%E4%B8%8E%E9%87%91%E7%94%B0%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84_%E6%B7%B1%E5%9C%B3%E4%B8%AD%E5%BF%83%E5%A4%A9%E5%85%83%E5%85%AC%E5%AF%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="269">
@@ -27055,9 +27055,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G269">
+      <c r="G269" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E9%87%91%E7%94%B0%E8%B7%AF3090%E5%8F%B7_%E4%BC%9A%E5%B1%95%E4%B8%AD%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A1%E5%8F%A3%E6%AD%A5%E8%A1%8C340%E7%B1%B3_%E7%A6%8F%E5%B2%97%E5%9B%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="270">
@@ -27091,9 +27091,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G270">
+      <c r="G270" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E9%87%91%E7%94%B0%E8%B7%AF3090%E5%8F%B7_%E4%BC%9A%E5%B1%95%E4%B8%AD%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A1%E5%8F%A3%E6%AD%A5%E8%A1%8C340%E7%B1%B3_%E7%A6%8F%E5%B2%97%E5%9B%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="271">
@@ -27127,9 +27127,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G271">
+      <c r="G271" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E9%87%91%E7%94%B0%E8%B7%AF3090%E5%8F%B7_%E4%BC%9A%E5%B1%95%E4%B8%AD%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A1%E5%8F%A3%E6%AD%A5%E8%A1%8C340%E7%B1%B3_%E7%A6%8F%E5%B2%97%E5%9B%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="272">
@@ -27163,9 +27163,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G272">
+      <c r="G272" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E9%87%91%E7%94%B0%E8%B7%AF3090%E5%8F%B7_%E4%BC%9A%E5%B1%95%E4%B8%AD%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A1%E5%8F%A3%E6%AD%A5%E8%A1%8C340%E7%B1%B3_%E7%A6%8F%E5%B2%97%E5%9B%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="273">
@@ -27199,9 +27199,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G273">
+      <c r="G273" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E9%87%91%E7%94%B0%E8%B7%AF3090%E5%8F%B7_%E4%BC%9A%E5%B1%95%E4%B8%AD%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A1%E5%8F%A3%E6%AD%A5%E8%A1%8C340%E7%B1%B3_%E7%A6%8F%E5%B2%97%E5%9B%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="274">
@@ -27235,9 +27235,9 @@
           <t>（5）暂存点存在用水用电安全隐患(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G274">
+      <c r="G274" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA_%E9%87%91%E7%94%B0%E8%B7%AF3090%E5%8F%B7_%E4%BC%9A%E5%B1%95%E4%B8%AD%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A1%E5%8F%A3%E6%AD%A5%E8%A1%8C340%E7%B1%B3_%E7%A6%8F%E5%B2%97%E5%9B%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="275">
@@ -27271,9 +27271,9 @@
           <t>（2）未按要求张贴垃圾分类宣传海报/指引，或海报内容错误/未更新等(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G275">
+      <c r="G275" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99_%E5%B2%97%E5%8E%A6%E5%9C%B0%E9%93%81%E7%AB%99.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="276">
@@ -27307,9 +27307,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G276">
+      <c r="G276" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="277">
@@ -27343,9 +27343,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G277">
+      <c r="G277" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="278">
@@ -27379,9 +27379,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G278">
+      <c r="G278" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="279">
@@ -27415,9 +27415,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G279">
+      <c r="G279" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="280">
@@ -27451,9 +27451,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G280">
+      <c r="G280" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="281">
@@ -27487,9 +27487,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G281">
+      <c r="G281" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="282">
@@ -27523,9 +27523,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G282">
+      <c r="G282" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="283">
@@ -27559,9 +27559,9 @@
           <t>（3）暂存点与专项垃圾暂存点共用的，应保留一部分位置存放专项垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G283">
+      <c r="G283" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%A6%8F%E7%94%B0%E5%8C%BA%E6%B7%B1%E5%8D%97%E5%A4%A7%E9%81%932001%E5%8F%B7_%E5%98%89%E9%BA%9F%E8%B1%AA%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="284">
@@ -27595,9 +27595,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G284">
+      <c r="G284" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E8%8A%B1%E5%9B%AD_%E6%B7%B1%E5%8D%97%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="285">
@@ -27631,9 +27631,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）； （7）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G285">
+      <c r="G285" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E8%8A%B1%E5%9B%AD_%E6%B7%B1%E5%8D%97%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="286">
@@ -27667,9 +27667,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）； （3）暂存点与专项垃圾暂存点共用的，应保留一部分位置存放专项垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G286">
+      <c r="G286" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B7%B1%E5%8D%97%E8%8A%B1%E5%9B%AD_%E6%B7%B1%E5%8D%97%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="287">
@@ -27703,9 +27703,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G287">
+      <c r="G287" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91_%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="288">
@@ -27739,9 +27739,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G288">
+      <c r="G288" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91_%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="289">
@@ -27775,9 +27775,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G289">
+      <c r="G289" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91_%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="290">
@@ -27811,9 +27811,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G290">
+      <c r="G290" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91_%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="291">
@@ -27847,9 +27847,9 @@
           <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G291">
+      <c r="G291" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91_%E6%B1%87%E6%99%AF%E8%B1%AA%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="292">
@@ -27883,9 +27883,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G292">
+      <c r="G292" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E5%85%B4%E8%B7%AF6%E5%8F%B7%E7%A7%91%E8%8B%91%E8%A5%BF%E4%BD%8F%E5%AE%85%E5%B0%8F%E5%8C%BA_%E7%A7%91%E8%8B%91%E8%A5%BF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="293">
@@ -27919,9 +27919,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G293">
+      <c r="G293" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E5%85%B4%E8%B7%AF6%E5%8F%B7%E7%A7%91%E8%8B%91%E8%A5%BF%E4%BD%8F%E5%AE%85%E5%B0%8F%E5%8C%BA_%E7%A7%91%E8%8B%91%E8%A5%BF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="294">
@@ -27955,9 +27955,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G294">
+      <c r="G294" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E5%85%B4%E8%B7%AF6%E5%8F%B7%E7%A7%91%E8%8B%91%E8%A5%BF%E4%BD%8F%E5%AE%85%E5%B0%8F%E5%8C%BA_%E7%A7%91%E8%8B%91%E8%A5%BF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="295">
@@ -27991,9 +27991,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G295">
+      <c r="G295" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E5%85%B4%E8%B7%AF6%E5%8F%B7%E7%A7%91%E8%8B%91%E8%A5%BF%E4%BD%8F%E5%AE%85%E5%B0%8F%E5%8C%BA_%E7%A7%91%E8%8B%91%E8%A5%BF%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="296">
@@ -28027,9 +28027,9 @@
           <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G296">
+      <c r="G296" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A7%91%E5%8F%91%E8%B7%AF10%E5%8F%B7_%E7%BB%B4%E7%94%A8%E7%BB%BC%E5%90%88%E6%A5%BC%E7%A7%91%E8%8B%91%E5%B1%85%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="297">
@@ -28063,9 +28063,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G297">
+      <c r="G297" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A7%91%E5%8F%91%E8%B7%AF10%E5%8F%B7_%E7%BB%B4%E7%94%A8%E7%BB%BC%E5%90%88%E6%A5%BC%E7%A7%91%E8%8B%91%E5%B1%85%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="298">
@@ -28099,9 +28099,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G298">
+      <c r="G298" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A7%91%E5%8F%91%E8%B7%AF10%E5%8F%B7_%E7%BB%B4%E7%94%A8%E7%BB%BC%E5%90%88%E6%A5%BC%E7%A7%91%E8%8B%91%E5%B1%85%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="299">
@@ -28135,9 +28135,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G299">
+      <c r="G299" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A7%91%E5%8F%91%E8%B7%AF10%E5%8F%B7_%E7%BB%B4%E7%94%A8%E7%BB%BC%E5%90%88%E6%A5%BC%E7%A7%91%E8%8B%91%E5%B1%85%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="300">
@@ -28171,9 +28171,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G300">
+      <c r="G300" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A7%91%E5%8F%91%E8%B7%AF10%E5%8F%B7_%E7%BB%B4%E7%94%A8%E7%BB%BC%E5%90%88%E6%A5%BC%E7%A7%91%E8%8B%91%E5%B1%85%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="301">
@@ -28207,9 +28207,9 @@
           <t>（2）未成组摆放两分类收集容器；(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G301">
+      <c r="G301" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E8%8B%91%E8%B7%AF16%E5%8F%B7%E4%B8%9C%E6%96%B9%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6_%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E6%96%B9%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="302">
@@ -28243,9 +28243,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G302">
+      <c r="G302" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E8%8B%91%E8%B7%AF16%E5%8F%B7%E4%B8%9C%E6%96%B9%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6_%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E6%96%B9%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="303">
@@ -28279,9 +28279,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G303">
+      <c r="G303" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%A7%91%E8%8B%91%E8%B7%AF16%E5%8F%B7%E4%B8%9C%E6%96%B9%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6_%E6%B7%B1%E5%9C%B3%E5%B8%82%E4%B8%9C%E6%96%B9%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="304">
@@ -28315,9 +28315,9 @@
           <t>（2）责任公示牌缺失(-2)（1处问题）； （3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G304">
+      <c r="G304" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A4%BE%E5%8C%BA%E8%AD%A6%E5%8A%A1%E5%AE%A4%E7%A7%91%E8%8B%91%E8%8A%B1%E5%9B%AD_%E7%A7%91%E5%8D%8E%E8%B7%AF_%E7%A7%91%E8%8B%91%E4%B8%9C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="305">
@@ -28351,9 +28351,9 @@
           <t>（4）其他问题（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G305">
+      <c r="G305" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A4%BE%E5%8C%BA%E8%AD%A6%E5%8A%A1%E5%AE%A4%E7%A7%91%E8%8B%91%E8%8A%B1%E5%9B%AD_%E7%A7%91%E5%8D%8E%E8%B7%AF_%E7%A7%91%E8%8B%91%E4%B8%9C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="306">
@@ -28387,9 +28387,9 @@
           <t>（4）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G306">
+      <c r="G306" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E7%A7%91%E6%8A%80%E5%9B%AD%E7%A4%BE%E5%8C%BA%E8%AD%A6%E5%8A%A1%E5%AE%A4%E7%A7%91%E8%8B%91%E8%8A%B1%E5%9B%AD_%E7%A7%91%E5%8D%8E%E8%B7%AF_%E7%A7%91%E8%8B%91%E4%B8%9C%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="307">
@@ -28423,9 +28423,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G307">
+      <c r="G307" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%A1%91%E8%BE%BE%E8%8B%91_%E6%A1%91%E8%BE%BE%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="308">
@@ -28459,9 +28459,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G308">
+      <c r="G308" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%A1%91%E8%BE%BE%E8%8B%91_%E6%A1%91%E8%BE%BE%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="309">
@@ -28495,9 +28495,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G309">
+      <c r="G309" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E7%B2%A4%E6%B5%B7%E8%A1%97%E9%81%93%E6%A1%91%E8%BE%BE%E8%8B%91_%E6%A1%91%E8%BE%BE%E8%8B%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="310">
@@ -28531,9 +28531,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G310">
+      <c r="G310" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E9%AB%98%E7%A7%91%E5%A4%A7%E9%81%9388%E5%8F%B7%E5%8D%97%E6%99%AF%E5%8D%97%E7%BA%A6%E6%96%B0%E6%9D%91_%E5%8D%97%E6%99%AF%E5%8D%97%E7%BA%A6%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="311">
@@ -28567,9 +28567,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G311">
+      <c r="G311" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E9%AB%98%E7%A7%91%E5%A4%A7%E9%81%9388%E5%8F%B7%E5%8D%97%E6%99%AF%E5%8D%97%E7%BA%A6%E6%96%B0%E6%9D%91_%E5%8D%97%E6%99%AF%E5%8D%97%E7%BA%A6%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="312">
@@ -28603,9 +28603,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G312">
+      <c r="G312" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%91%B5%E5%8D%97%E8%B7%AF110%E7%9F%B3%E6%A1%A5%E5%A4%B4%E5%B0%8F%E5%8C%BA_%E7%9F%B3%E6%A1%A5%E5%A4%B4.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="313">
@@ -28639,9 +28639,9 @@
           <t>（2）投放点未安装智慧视频监控设备(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G313">
+      <c r="G313" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%91%B5%E5%8D%97%E8%B7%AF110%E7%9F%B3%E6%A1%A5%E5%A4%B4%E5%B0%8F%E5%8C%BA_%E7%9F%B3%E6%A1%A5%E5%A4%B4.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="314">
@@ -28675,9 +28675,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G314">
+      <c r="G314" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%91%B5%E5%8D%97%E8%B7%AF110%E7%9F%B3%E6%A1%A5%E5%A4%B4%E5%B0%8F%E5%8C%BA_%E7%9F%B3%E6%A1%A5%E5%A4%B4.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="315">
@@ -28711,9 +28711,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G315">
+      <c r="G315" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%91%B5%E5%8D%97%E8%B7%AF110%E7%9F%B3%E6%A1%A5%E5%A4%B4%E5%B0%8F%E5%8C%BA_%E7%9F%B3%E6%A1%A5%E5%A4%B4.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="316">
@@ -28747,9 +28747,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G316">
+      <c r="G316" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%91%B5%E5%8D%97%E8%B7%AF110%E7%9F%B3%E6%A1%A5%E5%A4%B4%E5%B0%8F%E5%8C%BA_%E7%9F%B3%E6%A1%A5%E5%A4%B4.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="317">
@@ -28783,9 +28783,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G317">
+      <c r="G317" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%91%B5%E5%8D%97%E8%B7%AF110%E7%9F%B3%E6%A1%A5%E5%A4%B4%E5%B0%8F%E5%8C%BA_%E7%9F%B3%E6%A1%A5%E5%A4%B4.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="318">
@@ -28819,9 +28819,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G318">
+      <c r="G318" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E8%91%B5%E5%8D%97%E8%B7%AF110%E7%9F%B3%E6%A1%A5%E5%A4%B4%E5%B0%8F%E5%8C%BA_%E7%9F%B3%E6%A1%A5%E5%A4%B4.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="319">
@@ -28855,9 +28855,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G319">
+      <c r="G319" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E8%81%94%E5%92%8C%E5%8A%9E%E5%85%AC%E5%AE%A4201_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E8%81%94%E5%92%8C%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="320">
@@ -28891,9 +28891,9 @@
           <t>（2）未使用(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G320">
+      <c r="G320" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%AE%9D%E9%BE%99%E8%A1%97%E9%81%93%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E8%81%94%E5%92%8C%E5%8A%9E%E5%85%AC%E5%AE%A4201_%E5%8D%97%E7%BA%A6%E7%A4%BE%E5%8C%BA%E8%81%94%E5%92%8C%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="321">
@@ -28927,9 +28927,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G321">
+      <c r="G321" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A4%A7%E9%B9%8F%E6%96%B0%E5%8C%BA%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E8%B7%AF84%E5%8F%B7_%E6%96%B0%E5%B1%8B%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="322">
@@ -28963,9 +28963,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G322">
+      <c r="G322" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A4%A7%E9%B9%8F%E6%96%B0%E5%8C%BA%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E8%B7%AF84%E5%8F%B7_%E6%96%B0%E5%B1%8B%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="323">
@@ -28999,9 +28999,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G323">
+      <c r="G323" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A4%A7%E9%B9%8F%E6%96%B0%E5%8C%BA%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E8%B7%AF84%E5%8F%B7_%E6%96%B0%E5%B1%8B%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="324">
@@ -29035,9 +29035,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G324">
+      <c r="G324" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A4%A7%E9%B9%8F%E6%96%B0%E5%8C%BA%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E8%B7%AF84%E5%8F%B7_%E6%96%B0%E5%B1%8B%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="325">
@@ -29071,9 +29071,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G325">
+      <c r="G325" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B8%83%E6%96%B0%E8%B7%AF91_5_%E5%B8%83%E9%94%A6%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="326">
@@ -29107,9 +29107,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G326">
+      <c r="G326" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B8%83%E6%96%B0%E8%B7%AF91_5_%E5%B8%83%E9%94%A6%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="327">
@@ -29143,9 +29143,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G327">
+      <c r="G327" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B8%83%E6%96%B0%E8%B7%AF91_5_%E5%B8%83%E9%94%A6%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="328">
@@ -29179,9 +29179,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G328">
+      <c r="G328" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B8%83%E6%96%B0%E8%B7%AF130%E5%8F%B7_%E5%8D%97%E5%9D%91%E5%9F%94.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="329">
@@ -29215,9 +29215,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G329">
+      <c r="G329" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E7%BB%9F%E5%BB%BA%E6%A5%BC_%E5%B8%83%E6%96%B0%E7%BB%9F%E5%BB%BA%E6%A5%BC.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="330">
@@ -29251,9 +29251,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G330">
+      <c r="G330" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E7%BB%9F%E5%BB%BA%E6%A5%BC_%E5%B8%83%E6%96%B0%E7%BB%9F%E5%BB%BA%E6%A5%BC.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="331">
@@ -29287,9 +29287,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G331">
+      <c r="G331" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E7%A4%BE%E5%8C%BA%E6%B0%B4%E8%B4%9D%E6%9D%91_%E6%B0%B4%E8%B4%9D%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="332">
@@ -29323,9 +29323,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G332">
+      <c r="G332" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%A4%A7%E9%B9%8F%E8%A1%97%E9%81%93%E5%B8%83%E6%96%B0%E7%A4%BE%E5%8C%BA%E6%B0%B4%E8%B4%9D%E6%9D%91_%E6%B0%B4%E8%B4%9D%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="333">
@@ -29359,9 +29359,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G333">
+      <c r="G333" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E5%8D%93%E8%B6%8A%E7%9A%87%E5%90%8E%E9%81%93_%E5%8D%93%E8%B6%8A%E7%9A%87%E5%90%8E%E9%81%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="334">
@@ -29395,9 +29395,9 @@
           <t>（5）其他问题(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G334">
+      <c r="G334" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E5%8D%93%E8%B6%8A%E7%9A%87%E5%90%8E%E9%81%93_%E5%8D%93%E8%B6%8A%E7%9A%87%E5%90%8E%E9%81%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="335">
@@ -29431,9 +29431,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G335">
+      <c r="G335" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E5%8D%93%E8%B6%8A%E7%9A%87%E5%90%8E%E9%81%93_%E5%8D%93%E8%B6%8A%E7%9A%87%E5%90%8E%E9%81%93.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="336">
@@ -29467,9 +29467,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G336">
+      <c r="G336" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E9%A3%9E%E5%A4%A7%E9%81%9310%E5%8F%B7_%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E4%BA%8C%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="337">
@@ -29503,9 +29503,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G337">
+      <c r="G337" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E9%A3%9E%E5%A4%A7%E9%81%9310%E5%8F%B7_%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E4%BA%8C%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="338">
@@ -29539,9 +29539,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G338">
+      <c r="G338" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E7%88%B1%E8%81%94%E7%A4%BE%E5%8C%BA%E7%88%B1%E5%8D%97%E8%B7%AF641%E5%8F%B7%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E8%8A%B1%E5%9B%AD_%E4%BA%94%E5%8C%BA_%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E4%BA%94%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="339">
@@ -29575,9 +29575,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G339">
+      <c r="G339" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E7%88%B1%E8%81%94%E7%A4%BE%E5%8C%BA%E7%88%B1%E5%8D%97%E8%B7%AF641%E5%8F%B7%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E8%8A%B1%E5%9B%AD_%E4%BA%94%E5%8C%BA_%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E4%BA%94%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="340">
@@ -29611,9 +29611,9 @@
           <t>（2）箱体未公示服务单位、服务电话、回收品类、回收价格等基本信息，回收电话不真实(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G340">
+      <c r="G340" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E7%88%B1%E8%81%94%E7%A4%BE%E5%8C%BA%E7%88%B1%E5%8D%97%E8%B7%AF641%E5%8F%B7%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E8%8A%B1%E5%9B%AD_%E4%BA%94%E5%8C%BA_%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E4%BA%94%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="341">
@@ -29647,9 +29647,9 @@
           <t>（2）标示错误信息(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G341">
+      <c r="G341" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E7%88%B1%E8%81%94%E7%A4%BE%E5%8C%BA%E7%88%B1%E5%8D%97%E8%B7%AF641%E5%8F%B7%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E8%8A%B1%E5%9B%AD_%E4%BA%94%E5%8C%BA_%E9%A2%90%E5%AE%89%E9%83%BD%E4%BC%9A%E4%B8%AD%E5%A4%AE%E4%BA%94%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="342">
@@ -29683,9 +29683,9 @@
           <t>（2）箱体未公示服务单位、服务电话、回收品类、回收价格等基本信息，回收电话不真实(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G342">
+      <c r="G342" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E7%88%B1%E5%8D%97%E8%B7%AF666%E5%8F%B7_%E6%98%9F%E6%B2%B3%E6%97%B6%E4%BB%A3%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="343">
@@ -29719,9 +29719,9 @@
           <t>（2）分类收集容器缺失(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G343">
+      <c r="G343" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%85%89%E7%8E%96%E6%82%A6%E5%8F%B0_%E9%BE%99%E5%85%89%E7%8E%96%E6%82%A6%E5%8F%B0.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="344">
@@ -29755,9 +29755,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G344">
+      <c r="G344" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%85%89%E7%8E%96%E6%82%A6%E5%8F%B0_%E9%BE%99%E5%85%89%E7%8E%96%E6%82%A6%E5%8F%B0.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="345">
@@ -29791,9 +29791,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G345">
+      <c r="G345" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%85%89%E7%8E%96%E6%82%A6%E5%8F%B0_%E9%BE%99%E5%85%89%E7%8E%96%E6%82%A6%E5%8F%B0.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="346">
@@ -29827,9 +29827,9 @@
           <t>（4）其他问题（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G346">
+      <c r="G346" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%95%BF%E5%9F%8E%E9%87%8C%E7%A8%8B%E5%AE%B6%E5%9B%AD_%E9%95%BF%E5%9F%8E%E9%87%8C%E7%A8%8B%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="347">
@@ -29863,9 +29863,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G347">
+      <c r="G347" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%95%BF%E5%9F%8E%E9%87%8C%E7%A8%8B%E5%AE%B6%E5%9B%AD_%E9%95%BF%E5%9F%8E%E9%87%8C%E7%A8%8B%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="348">
@@ -29899,9 +29899,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-4)（2处问题）</t>
         </is>
       </c>
-      <c r="G348">
+      <c r="G348" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%95%BF%E5%9F%8E%E9%87%8C%E7%A8%8B%E5%AE%B6%E5%9B%AD_%E9%95%BF%E5%9F%8E%E9%87%8C%E7%A8%8B%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="349">
@@ -29935,9 +29935,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G349">
+      <c r="G349" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E8%BF%9C%E6%99%AF%E5%AE%B6%E5%9B%AD_%E8%BF%9C%E6%99%AF%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="350">
@@ -29971,9 +29971,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G350">
+      <c r="G350" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E8%BF%9C%E6%99%AF%E5%AE%B6%E5%9B%AD_%E8%BF%9C%E6%99%AF%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="351">
@@ -30007,9 +30007,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G351">
+      <c r="G351" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BB%84%E9%98%81%E8%B7%AF6%E5%8F%B7_%E5%9F%8E%E5%B8%82%E7%AB%8B%E6%96%B9%E8%8A%B1%E5%9B%AD_%E7%BB%BF%E6%99%AF%E5%A4%A7%E5%85%AC%E9%A6%86_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="352">
@@ -30043,9 +30043,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G352">
+      <c r="G352" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BB%84%E9%98%81%E8%B7%AF6%E5%8F%B7_%E5%9F%8E%E5%B8%82%E7%AB%8B%E6%96%B9%E8%8A%B1%E5%9B%AD_%E7%BB%BF%E6%99%AF%E5%A4%A7%E5%85%AC%E9%A6%86_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="353">
@@ -30079,9 +30079,9 @@
           <t>（2）箱体未公示服务单位、服务电话、回收品类、回收价格等基本信息，回收电话不真实(-1)（2处问题）</t>
         </is>
       </c>
-      <c r="G353">
+      <c r="G353" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BB%84%E9%98%81%E8%B7%AF6%E5%8F%B7_%E5%9F%8E%E5%B8%82%E7%AB%8B%E6%96%B9%E8%8A%B1%E5%9B%AD_%E7%BB%BF%E6%99%AF%E5%A4%A7%E5%85%AC%E9%A6%86_.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="354">
@@ -30115,9 +30115,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G354">
+      <c r="G354" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E6%B2%99%E5%9B%AD%E8%B7%AF%E4%B8%8E%E9%85%8D%E5%A5%97%E4%BA%8C%E8%B7%AF%E4%BA%A4%E5%8F%89%E8%B7%AF%E5%8F%A3%E5%BE%80%E4%B8%9C%E5%8D%97%E7%BA%A6100%E7%B1%B3_%E9%98%B3%E5%85%89%E5%A4%A9%E5%81%A5%E5%9F%8E%E4%B8%9C%E5%8D%97%E4%BE%A7%E7%BA%A650%E7%B1%B3_%E4%B8%AD%E6%A3%AE%E5%8F%8C%E5%AD%90%E5%BA%A7%E5%85%AC%E9%A6%86.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="355">
@@ -30151,9 +30151,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G355">
+      <c r="G355" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E6%B2%99%E5%9B%AD%E8%B7%AF%E4%B8%8E%E9%85%8D%E5%A5%97%E4%BA%8C%E8%B7%AF%E4%BA%A4%E5%8F%89%E8%B7%AF%E5%8F%A3%E5%BE%80%E4%B8%9C%E5%8D%97%E7%BA%A6100%E7%B1%B3_%E9%98%B3%E5%85%89%E5%A4%A9%E5%81%A5%E5%9F%8E%E4%B8%9C%E5%8D%97%E4%BE%A7%E7%BA%A650%E7%B1%B3_%E4%B8%AD%E6%A3%AE%E5%8F%8C%E5%AD%90%E5%BA%A7%E5%85%AC%E9%A6%86.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="356">
@@ -30187,9 +30187,9 @@
           <t>（2）收集容器缺失(-6)（1处问题）</t>
         </is>
       </c>
-      <c r="G356">
+      <c r="G356" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%88%B1%E8%81%94%E7%A4%BE%E5%8C%BA%E5%89%8D%E8%BF%9B%E5%95%86%E4%B8%9A%E5%B9%BF%E5%9C%BA_%E5%8D%8E%E8%AE%B0%E5%86%9C%E5%AE%B6%E8%8F%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="357">
@@ -30223,9 +30223,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G357">
+      <c r="G357" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%88%B1%E8%81%94%E7%A4%BE%E5%8C%BA%E5%89%8D%E8%BF%9B%E5%95%86%E4%B8%9A%E5%B9%BF%E5%9C%BA_%E5%8D%8E%E8%AE%B0%E5%86%9C%E5%AE%B6%E8%8F%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="358">
@@ -30259,9 +30259,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G358">
+      <c r="G358" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E9%BE%99%E5%9F%8E%E8%A1%97%E9%81%93%E6%98%9F%E6%B2%B3%E6%97%B6%E4%BB%A3%E6%98%9F%E6%B2%B3COCO_Park_%E9%BE%99%E5%B2%97%E5%BA%97_%E9%BE%99%E5%B2%97%E6%98%9F%E6%B2%B3cocopark.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="359">
@@ -30295,9 +30295,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G359">
+      <c r="G359" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD_%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="360">
@@ -30331,9 +30331,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G360">
+      <c r="G360" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD_%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="361">
@@ -30367,9 +30367,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G361">
+      <c r="G361" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD_%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="362">
@@ -30403,9 +30403,9 @@
           <t>（5）暂存点存在用水用电安全隐患(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G362">
+      <c r="G362" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD_%E7%BF%94%E9%BE%99%E5%BE%A1%E5%BA%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="363">
@@ -30439,9 +30439,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G363">
+      <c r="G363" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%A4%A7%E5%8F%91%E5%9F%94%E7%A4%BE%E5%8C%BA%E5%88%9B%E5%85%B4%E6%97%B6%E4%BB%A3_%E5%88%9B%E5%85%B4%E6%97%B6%E4%BB%A3.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="364">
@@ -30475,9 +30475,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G364">
+      <c r="G364" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%A4%A7%E5%8F%91%E5%9F%94%E7%A4%BE%E5%8C%BA%E5%88%9B%E5%85%B4%E6%97%B6%E4%BB%A3_%E5%88%9B%E5%85%B4%E6%97%B6%E4%BB%A3.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="365">
@@ -30511,9 +30511,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G365">
+      <c r="G365" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%B2%97%E5%8C%BA%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%A4%A7%E5%8F%91%E5%9F%94%E4%B8%9C%E6%9D%91%E4%B8%83%E5%B7%B711_12%E5%8F%B7%E4%B8%80_%E4%BA%8C%E6%A5%BC_%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E7%AC%AC%E4%BA%8C%E4%BA%BA%E6%B0%91%E5%8C%BB%E9%99%A2%E5%A4%A7%E5%8F%91%E5%9F%94%E7%A4%BE%E5%8C%BA%E5%81%A5%E5%BA%B7%E6%9C%8D%E5%8A%A1%E4%B8%AD%E5%BF%83.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="366">
@@ -30547,9 +30547,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G366">
+      <c r="G366" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%90%89%E5%8D%8E%E8%B7%AF%E4%B8%8E%E4%BA%94%E5%92%8C%E5%A4%A7%E9%81%93%E4%BA%A4%E6%B1%87%E5%A4%84%E8%A5%BF%E5%8D%97%E8%A7%92_%E4%BD%B3%E5%8D%8E%E9%A2%86%E6%B1%87.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="367">
@@ -30583,9 +30583,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G367">
+      <c r="G367" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%90%89%E5%8D%8E%E8%B7%AF%E4%B8%8E%E4%BA%94%E5%92%8C%E5%A4%A7%E9%81%93%E4%BA%A4%E6%B1%87%E5%A4%84%E8%A5%BF%E5%8D%97%E8%A7%92_%E4%BD%B3%E5%8D%8E%E9%A2%86%E6%B1%87.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="368">
@@ -30619,9 +30619,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G368">
+      <c r="G368" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%90%89%E5%8D%8E%E8%B7%AF%E4%B8%8E%E4%BA%94%E5%92%8C%E5%A4%A7%E9%81%93%E4%BA%A4%E6%B1%87%E5%A4%84%E8%A5%BF%E5%8D%97%E8%A7%92_%E4%BD%B3%E5%8D%8E%E9%A2%86%E6%B1%87.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="369">
@@ -30655,9 +30655,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G369">
+      <c r="G369" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA_%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="370">
@@ -30691,9 +30691,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G370">
+      <c r="G370" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA_%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="371">
@@ -30727,9 +30727,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G371">
+      <c r="G371" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA_%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="372">
@@ -30763,9 +30763,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G372">
+      <c r="G372" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA_%E8%A5%BF%E8%BE%B9%E6%96%B0%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="373">
@@ -30799,9 +30799,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）； （3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G373">
+      <c r="G373" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E8%A5%BF%E6%B6%8C%E4%B8%89%E8%B7%AF_%E8%A5%BF%E8%BE%B9%E6%97%A7%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="374">
@@ -30835,9 +30835,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G374">
+      <c r="G374" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E8%A5%BF%E6%B6%8C%E4%B8%89%E8%B7%AF_%E8%A5%BF%E8%BE%B9%E6%97%A7%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="375">
@@ -30871,9 +30871,9 @@
           <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
         </is>
       </c>
-      <c r="G375">
+      <c r="G375" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E8%A5%BF%E6%B6%8C%E4%B8%89%E8%B7%AF_%E8%A5%BF%E8%BE%B9%E6%97%A7%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="376">
@@ -30907,9 +30907,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G376">
+      <c r="G376" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%AE%9D%E5%AE%89%E5%9B%B4%E5%90%8E%E5%BA%95%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E5%90%8E%E5%BA%95%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="377">
@@ -30943,9 +30943,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G377">
+      <c r="G377" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%AE%9D%E5%AE%89%E5%9B%B4%E5%90%8E%E5%BA%95%E5%B0%8F%E5%8C%BA_%E5%9B%B4%E5%90%8E%E5%BA%95%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="378">
@@ -30979,9 +30979,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G378">
+      <c r="G378" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E8%A5%BF%E6%B6%8C%E4%B8%89%E8%B7%AF50%E5%8F%B7%E4%BF%A1%E5%BE%B7_%E5%8D%A7%E9%BE%99%E5%9B%AD_%E8%8F%9C%E5%9B%AD%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="379">
@@ -31015,9 +31015,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G379">
+      <c r="G379" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E7%A5%A0%E5%A0%82%E5%8D%97%E5%8C%97%E5%8C%BA_%E7%A5%A0%E5%A0%82%E5%8D%97%E5%8C%97%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="380">
@@ -31051,9 +31051,9 @@
           <t>（2）洗手设施缺失(-1)（1处问题）</t>
         </is>
       </c>
-      <c r="G380">
+      <c r="G380" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E7%A5%A0%E5%A0%82%E5%8D%97%E5%8C%97%E5%8C%BA_%E7%A5%A0%E5%A0%82%E5%8D%97%E5%8C%97%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="381">
@@ -31087,9 +31087,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G381">
+      <c r="G381" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E7%A5%A0%E5%A0%82%E5%8D%97%E5%8C%97%E5%8C%BA_%E7%A5%A0%E5%A0%82%E5%8D%97%E5%8C%97%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="382">
@@ -31123,9 +31123,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G382">
+      <c r="G382" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%8C%AF%E5%85%B4%E8%B7%AF29%E5%8F%B7_%E5%B2%97%E7%93%A6%E5%9F%94%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="383">
@@ -31159,9 +31159,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G383">
+      <c r="G383" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%8C%AF%E5%85%B4%E8%B7%AF29%E5%8F%B7_%E5%B2%97%E7%93%A6%E5%9F%94%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="384">
@@ -31195,9 +31195,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G384">
+      <c r="G384" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E5%9F%94%E5%A4%B4%E6%A1%A5%E5%B0%8F%E5%8C%BA_%E5%9F%94%E5%A4%B4%E6%A1%A5%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="385">
@@ -31231,9 +31231,9 @@
           <t>（3）视频监控安装角度不正确(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G385">
+      <c r="G385" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E5%9F%94%E5%A4%B4%E6%A1%A5%E5%B0%8F%E5%8C%BA_%E5%9F%94%E5%A4%B4%E6%A1%A5%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="386">
@@ -31267,9 +31267,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G386">
+      <c r="G386" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%B2%99%E4%BA%95%E8%A1%97%E9%81%93%E6%AD%A5%E6%B6%8C%E7%A4%BE%E5%8C%BA%E5%A4%A7%E5%9B%AD%E6%A0%B9%E4%B8%80%E8%B7%AF_%E5%A4%A7%E5%9B%AD%E6%A0%B9.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="387">
@@ -31303,9 +31303,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G387">
+      <c r="G387" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1062%E5%8F%B7_%E6%80%A1%E9%83%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="388">
@@ -31339,9 +31339,9 @@
           <t>（3）内桶未开盖(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G388">
+      <c r="G388" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1062%E5%8F%B7_%E6%80%A1%E9%83%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="389">
@@ -31375,9 +31375,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G389">
+      <c r="G389" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1062%E5%8F%B7_%E6%80%A1%E9%83%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="390">
@@ -31411,9 +31411,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G390">
+      <c r="G390" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1062%E5%8F%B7_%E6%80%A1%E9%83%BD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="391">
@@ -31447,9 +31447,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G391">
+      <c r="G391" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1066%E5%8F%B7_%E5%9B%BD%E6%97%85%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="392">
@@ -31483,9 +31483,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G392">
+      <c r="G392" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1066%E5%8F%B7_%E5%9B%BD%E6%97%85%E5%AE%BF%E8%88%8D.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="393">
@@ -31519,9 +31519,9 @@
           <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G393">
+      <c r="G393" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1021%E5%8F%B7_%E5%8F%8C%E5%9F%8E%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="394">
@@ -31555,9 +31555,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G394">
+      <c r="G394" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1021%E5%8F%B7_%E5%8F%8C%E5%9F%8E%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="395">
@@ -31591,9 +31591,9 @@
           <t>（1）存在问题(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G395">
+      <c r="G395" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1021%E5%8F%B7_%E5%8F%8C%E5%9F%8E%E4%B8%96%E7%BA%AA%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="396">
@@ -31627,9 +31627,9 @@
           <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G396">
+      <c r="G396" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1025%E5%8F%B7_%E6%B1%87%E6%B3%B0%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="397">
@@ -31663,9 +31663,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G397">
+      <c r="G397" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1025%E5%8F%B7_%E6%B1%87%E6%B3%B0%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="398">
@@ -31699,9 +31699,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G398">
+      <c r="G398" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%B2%BF%E6%B2%B3%E5%8D%97%E8%B7%AF1025%E5%8F%B7_%E6%B1%87%E6%B3%B0%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="399">
@@ -31735,9 +31735,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G399">
+      <c r="G399" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%90%89%E5%8D%8E%E8%B7%AF696%E5%8F%B7%E5%9D%82%E7%94%B0%E5%A4%A9%E8%99%B9%E5%95%86%E5%9C%BA_%E5%A4%A9%E8%99%B9%E6%95%B0%E7%A7%91%E5%95%86%E4%B8%9A%E8%82%A1%E4%BB%BD%E6%9C%89%E9%99%90%E5%85%AC%E5%8F%B8%E5%9D%82%E7%94%B0%E5%A4%A9%E8%99%B9%E5%95%86%E5%9C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="400">
@@ -31771,9 +31771,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（4处问题）</t>
         </is>
       </c>
-      <c r="G400">
+      <c r="G400" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%BE%99%E5%A1%98%E6%9D%91_%E9%BE%99%E5%A1%98%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="401">
@@ -31807,9 +31807,9 @@
           <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G401">
+      <c r="G401" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%BE%99%E5%A1%98%E6%9D%91_%E9%BE%99%E5%A1%98%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="402">
@@ -31843,9 +31843,9 @@
           <t>（2）柜门未保持关闭(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G402">
+      <c r="G402" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%BE%99%E5%A1%98%E6%9D%91_%E9%BE%99%E5%A1%98%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="403">
@@ -31879,9 +31879,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G403">
+      <c r="G403" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%BE%99%E5%A1%98%E6%9D%91_%E9%BE%99%E5%A1%98%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="404">
@@ -31915,9 +31915,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G404">
+      <c r="G404" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E9%BE%99%E5%A1%98%E6%9D%91_%E9%BE%99%E5%A1%98%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="405">
@@ -31951,9 +31951,9 @@
           <t>（2）洗手设施缺失(-1)（2处问题）； （3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（3处问题）</t>
         </is>
       </c>
-      <c r="G405">
+      <c r="G405" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91%E6%B7%B1%E5%9C%B3%E9%BE%99%E8%B1%AA%E9%85%92%E5%BA%97_%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="406">
@@ -31987,9 +31987,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G406">
+      <c r="G406" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91%E6%B7%B1%E5%9C%B3%E9%BE%99%E8%B1%AA%E9%85%92%E5%BA%97_%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="407">
@@ -32023,9 +32023,9 @@
           <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G407">
+      <c r="G407" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91%E6%B7%B1%E5%9C%B3%E9%BE%99%E8%B1%AA%E9%85%92%E5%BA%97_%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="408">
@@ -32059,9 +32059,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
         </is>
       </c>
-      <c r="G408">
+      <c r="G408" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91%E6%B7%B1%E5%9C%B3%E9%BE%99%E8%B1%AA%E9%85%92%E5%BA%97_%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="409">
@@ -32095,9 +32095,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G409">
+      <c r="G409" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91%E6%B7%B1%E5%9C%B3%E9%BE%99%E8%B1%AA%E9%85%92%E5%BA%97_%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="410">
@@ -32131,9 +32131,9 @@
           <t>（2）未在黄线划定区域内(-2)（1处问题）； （3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G410">
+      <c r="G410" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91%E6%B7%B1%E5%9C%B3%E9%BE%99%E8%B1%AA%E9%85%92%E5%BA%97_%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="411">
@@ -32167,9 +32167,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G411">
+      <c r="G411" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91%E6%B7%B1%E5%9C%B3%E9%BE%99%E8%B1%AA%E9%85%92%E5%BA%97_%E9%BE%99%E5%A1%98%E6%96%B0%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="412">
@@ -32203,9 +32203,9 @@
           <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G412">
+      <c r="G412" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E6%B9%96%E5%BF%83%E5%A4%A7%E5%8E%A6_%E6%B9%96%E5%BF%83%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="413">
@@ -32239,9 +32239,9 @@
           <t>（4）误时投放点未开放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G413">
+      <c r="G413" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E6%B9%96%E5%BF%83%E5%A4%A7%E5%8E%A6_%E6%B9%96%E5%BF%83%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="414">
@@ -32275,9 +32275,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G414">
+      <c r="G414" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E6%B9%96%E5%BF%83%E5%A4%A7%E5%8E%A6_%E6%B9%96%E5%BF%83%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="415">
@@ -32311,9 +32311,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G415">
+      <c r="G415" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%98%A5%E9%A3%8E%E8%B7%AF2001%E5%8F%B7_%E5%8D%97%E5%8D%8E%E8%A1%97%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="416">
@@ -32347,9 +32347,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G416">
+      <c r="G416" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%98%A5%E9%A3%8E%E8%B7%AF2001%E5%8F%B7_%E5%8D%97%E5%8D%8E%E8%A1%97%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="417">
@@ -32383,9 +32383,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G417">
+      <c r="G417" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B9%96%E8%A1%97%E9%81%93%E6%98%A5%E9%A3%8E%E8%B7%AF2001%E5%8F%B7_%E5%8D%97%E5%8D%8E%E8%A1%97%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="418">
@@ -32419,9 +32419,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G418">
+      <c r="G418" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E6%B5%B7%E4%B8%B0%E8%8B%91_%E6%B5%B7%E4%B8%B0%E8%8B%91%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="419">
@@ -32455,9 +32455,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G419">
+      <c r="G419" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%8D%97%E6%B4%8B%E5%A4%A7%E5%8E%A6_%E5%8D%97%E6%B4%8B%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="420">
@@ -32491,9 +32491,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G420">
+      <c r="G420" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%98%89%E5%BE%A1%E8%B1%AA%E5%9B%AD_%E5%98%89%E5%BE%A1%E8%B1%AA%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="421">
@@ -32527,9 +32527,9 @@
           <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G421">
+      <c r="G421" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%98%89%E5%BE%A1%E8%B1%AA%E5%9B%AD_%E5%98%89%E5%BE%A1%E8%B1%AA%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="422">
@@ -32563,9 +32563,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G422">
+      <c r="G422" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%9D%82%E7%94%B0%E8%A1%97%E9%81%93%E5%98%89%E5%BE%A1%E8%B1%AA%E5%9B%AD_%E5%98%89%E5%BE%A1%E8%B1%AA%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="423">
@@ -32599,9 +32599,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G423">
+      <c r="G423" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA_%E6%B3%B0%E5%B1%B1%E8%B7%AF_%E5%BE%A1%E7%8F%91%E8%B1%AA%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="424">
@@ -32635,9 +32635,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（4处问题）</t>
         </is>
       </c>
-      <c r="G424">
+      <c r="G424" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA_%E6%B3%B0%E5%B1%B1%E8%B7%AF_%E5%BE%A1%E7%8F%91%E8%B1%AA%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="425">
@@ -32671,9 +32671,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G425">
+      <c r="G425" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%B2%97%E5%8C%BA_%E6%B3%B0%E5%B1%B1%E8%B7%AF_%E5%BE%A1%E7%8F%91%E8%B1%AA%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="426">
@@ -32707,9 +32707,9 @@
           <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（2处问题）</t>
         </is>
       </c>
-      <c r="G426">
+      <c r="G426" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E5%A4%A9%E5%81%A5%E7%A7%91%E6%8A%80%E5%A4%A7%E5%8E%A6_%E5%A4%A9%E5%81%A5%E4%BA%91%E9%80%94%E5%88%9B%E6%99%BA%E4%B8%AD%E5%BF%83.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="427">
@@ -32743,9 +32743,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G427">
+      <c r="G427" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8C%97%E7%8E%AF%E8%B7%AF%E4%B8%8E%E6%B7%B1%E4%BA%91%E8%B7%AF%E4%BA%A4%E7%95%8C%E5%A4%84_%E6%9C%97%E4%BE%A8%E5%B3%B0%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="428">
@@ -32779,9 +32779,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G428">
+      <c r="G428" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8C%97%E7%8E%AF%E8%B7%AF%E4%B8%8E%E6%B7%B1%E4%BA%91%E8%B7%AF%E4%BA%A4%E7%95%8C%E5%A4%84_%E6%9C%97%E4%BE%A8%E5%B3%B0%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="429">
@@ -32815,9 +32815,9 @@
           <t>（2）暂存点内垃圾清运不及时(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G429">
+      <c r="G429" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8C%97%E7%8E%AF%E8%B7%AF%E4%B8%8E%E6%B7%B1%E4%BA%91%E8%B7%AF%E4%BA%A4%E7%95%8C%E5%A4%84_%E6%9C%97%E4%BE%A8%E5%B3%B0%E5%B1%85.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="430">
@@ -32851,9 +32851,9 @@
           <t>否(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G430">
+      <c r="G430" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E6%B7%B1%E5%AE%89%E8%B7%AF33%E5%8F%B7%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C_%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="431">
@@ -32887,9 +32887,9 @@
           <t>（2）责任公示牌缺失(-2)（4处问题）</t>
         </is>
       </c>
-      <c r="G431">
+      <c r="G431" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E6%B7%B1%E5%AE%89%E8%B7%AF33%E5%8F%B7%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C_%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="432">
@@ -32923,9 +32923,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G432">
+      <c r="G432" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E6%B7%B1%E5%AE%89%E8%B7%AF33%E5%8F%B7%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C_%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="433">
@@ -32959,9 +32959,9 @@
           <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G433">
+      <c r="G433" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E6%B7%B1%E5%AE%89%E8%B7%AF33%E5%8F%B7%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C_%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="434">
@@ -32995,9 +32995,9 @@
           <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G434">
+      <c r="G434" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E6%B7%B1%E5%AE%89%E8%B7%AF33%E5%8F%B7%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C_%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="435">
@@ -33031,9 +33031,9 @@
           <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G435">
+      <c r="G435" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%8D%97%E5%B1%B1%E5%8C%BA%E6%B2%99%E6%B2%B3%E8%A1%97%E9%81%93%E6%B7%B1%E5%AE%89%E8%B7%AF33%E5%8F%B7%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C_%E6%B7%B1%E9%93%81%E6%87%BF%E5%BA%9C.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="436">
@@ -33067,9 +33067,9 @@
           <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（2处问题）； （3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G436">
+      <c r="G436" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91_%E7%AE%80%E4%B8%8A%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="437">
@@ -33103,9 +33103,9 @@
           <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（4处问题）</t>
         </is>
       </c>
-      <c r="G437">
+      <c r="G437" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91_%E7%AE%80%E4%B8%8A%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="438">
@@ -33139,9 +33139,9 @@
           <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（2处问题）</t>
         </is>
       </c>
-      <c r="G438">
+      <c r="G438" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91_%E7%AE%80%E4%B8%8A%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="439">
@@ -33175,9 +33175,9 @@
           <t>（5）其他问题(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G439">
+      <c r="G439" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91_%E7%AE%80%E4%B8%8A%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="440">
@@ -33211,9 +33211,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（3处问题）</t>
         </is>
       </c>
-      <c r="G440">
+      <c r="G440" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91_%E7%AE%80%E4%B8%8A%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="441">
@@ -33247,9 +33247,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G441">
+      <c r="G441" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91_%E7%AE%80%E4%B8%8A%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="442">
@@ -33283,9 +33283,9 @@
           <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G442">
+      <c r="G442" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91_%E7%AE%80%E4%B8%8A%E6%9D%91.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="443">
@@ -33319,9 +33319,9 @@
           <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G443">
+      <c r="G443" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91%E4%B8%8A%E4%B8%B0%E8%8A%B1%E5%9B%AD_%E4%B8%8A%E4%B8%B0%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="444">
@@ -33355,9 +33355,9 @@
           <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G444">
+      <c r="G444" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91%E4%B8%8A%E4%B8%B0%E8%8A%B1%E5%9B%AD_%E4%B8%8A%E4%B8%B0%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
     <row r="445">
@@ -33391,9 +33391,9 @@
           <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
         </is>
       </c>
-      <c r="G445">
+      <c r="G445" t="str">
         <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E9%BE%99%E5%8D%8E%E5%8C%BA%E6%B0%91%E6%B2%BB%E8%A1%97%E9%81%93%E9%BE%99%E5%A1%98%E7%A4%BE%E5%8C%BA%E7%AE%80%E4%B8%8A%E6%9D%91%E4%B8%8A%E4%B8%B0%E8%8A%B1%E5%9B%AD_%E4%B8%8A%E4%B8%B0%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
-        <v/>
+        <v>查看证据</v>
       </c>
     </row>
   </sheetData>

--- a/weeks/2026-09-03/巡查表.xlsx
+++ b/weeks/2026-09-03/巡查表.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:Z141"/>
+  <dimension ref="A2:Z171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17352,6 +17352,1737 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>港中旅花园二期</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>福田区农园路21号</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O142" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%BA%8C%E6%9C%9F.html","查看证据(2项/3张)")</f>
+        <v>查看证据(2项/3张)</v>
+      </c>
+      <c r="P142" t="n">
+        <v>96</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:35:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>港中旅花园一期</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>福田区农园路21号</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>1.4: 至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分） (-2)
+1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O143" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据(5项/8张)")</f>
+        <v>查看证据(5项/8张)</v>
+      </c>
+      <c r="P143" t="n">
+        <v>90</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:35:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>俊安苑</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>福田区农轩路121号</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O144" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E8%BD%A9%E8%B7%AF121%E5%8F%B7_%E4%BF%8A%E5%AE%89%E8%8B%91.html","查看证据(1项/2张)")</f>
+        <v>查看证据(1项/2张)</v>
+      </c>
+      <c r="P144" t="n">
+        <v>98</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:36:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>龙溪花园</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>福田区丰田路38号</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-4)
+1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+6.1: 公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O145" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF38%E5%8F%B7_%E9%BE%99%E6%BA%AA%E8%8A%B1%E5%9B%AD.html","查看证据(5项/8张)")</f>
+        <v>查看证据(5项/8张)</v>
+      </c>
+      <c r="P145" t="n">
+        <v>88</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:36:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>荔林苑</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>福田区红荔西路8076号</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>1.4: 至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分） (-2)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O146" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF8076%E5%8F%B7_%E8%8D%94%E6%9E%97%E8%8B%91.html","查看证据(5项/6张)")</f>
+        <v>查看证据(5项/6张)</v>
+      </c>
+      <c r="P146" t="n">
+        <v>90</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:41:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>香荔花园</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>福田区丰田路11号</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)</t>
+        </is>
+      </c>
+      <c r="O147" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF11%E5%8F%B7_%E9%A6%99%E8%8D%94%E8%8A%B1%E5%9B%AD.html","查看证据(1项/2张)")</f>
+        <v>查看证据(1项/2张)</v>
+      </c>
+      <c r="P147" t="n">
+        <v>98</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:41:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>海天一色</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>盐田区</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>盐田区海景二路8号</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O148" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF8%E5%8F%B7_%E6%B5%B7%E5%A4%A9%E4%B8%80%E8%89%B2.html","查看证据(3项/6张)")</f>
+        <v>查看证据(3项/6张)</v>
+      </c>
+      <c r="P148" t="n">
+        <v>94</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:41:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>香蜜天宝物华家园</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>福田区</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>福田区丰田路3号</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>1.4: 至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+5.5: 回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O149" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF3%E5%8F%B7_%E9%A6%99%E8%9C%9C%E5%A4%A9%E5%AE%9D%E7%89%A9%E5%8D%8E%E5%AE%B6%E5%9B%AD.html","查看证据(3项/4张)")</f>
+        <v>查看证据(3项/4张)</v>
+      </c>
+      <c r="P149" t="n">
+        <v>94</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:41:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>君临海域</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>盐田区</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>盐田区海景二路1015号</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O150" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1015%E5%8F%B7_%E5%90%9B%E4%B8%B4%E6%B5%B7%E5%9F%9F.html","查看证据(3项/7张)")</f>
+        <v>查看证据(3项/7张)</v>
+      </c>
+      <c r="P150" t="n">
+        <v>94</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:41:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>滨海花园</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>盐田区</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>深圳市盐田区海景路1号</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O151" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E8%B7%AF1%E5%8F%B7_%E6%BB%A8%E6%B5%B7%E8%8A%B1%E5%9B%AD.html","查看证据(1项/4张)")</f>
+        <v>查看证据(1项/4张)</v>
+      </c>
+      <c r="P151" t="n">
+        <v>98</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:42:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>壹海城</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>盐田区</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>盐田区深盐路与马庙等交汇处</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)</t>
+        </is>
+      </c>
+      <c r="O152" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B7%B1%E7%9B%90%E8%B7%AF%E4%B8%8E%E9%A9%AC%E5%BA%99%E7%AD%89%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%A3%B9%E6%B5%B7%E5%9F%8E.html","查看证据(1项/2张)")</f>
+        <v>查看证据(1项/2张)</v>
+      </c>
+      <c r="P152" t="n">
+        <v>98</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>壹海城V公馆</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>海景二路1038号</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.6: 设置洗手设施。（2分） (-1)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O153" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1038%E5%8F%B7_%E5%A3%B9%E6%B5%B7%E5%9F%8EV%E5%85%AC%E9%A6%86.html","查看证据(4项/8张)")</f>
+        <v>查看证据(4项/8张)</v>
+      </c>
+      <c r="P153" t="n">
+        <v>93</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>餐饮场所</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>八合里</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>海山路北面壹海MALL四层001号</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>1.1: 后厨区摆放可回收物、厨余垃圾、其他垃圾收集容器。（6分） (-6)
+1.3: 各类收集容器的分类标志完整、正确、清晰。 （18分） (-3)</t>
+        </is>
+      </c>
+      <c r="O154" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E5%B1%B1%E8%B7%AF%E5%8C%97%E9%9D%A2%E5%A3%B9%E6%B5%B7MALL%E5%9B%9B%E5%B1%82001%E5%8F%B7_%E5%85%AB%E5%90%88%E9%87%8C.html","查看证据(2项/5张)")</f>
+        <v>查看证据(2项/5张)</v>
+      </c>
+      <c r="P154" t="n">
+        <v>91</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>购物中心</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>华润万家超市</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>深盐路与海山路交汇处壹海道B1</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>2.2: 收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。 (-3)</t>
+        </is>
+      </c>
+      <c r="O155" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E7%9B%90%E8%B7%AF%E4%B8%8E%E6%B5%B7%E5%B1%B1%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E5%A3%B9%E6%B5%B7%E9%81%93B1_%E5%8D%8E%E6%B6%A6%E4%B8%87%E5%AE%B6%E8%B6%85%E5%B8%82.html","查看证据(1项/2张)")</f>
+        <v>查看证据(1项/2张)</v>
+      </c>
+      <c r="P155" t="n">
+        <v>97</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>酒店</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>雅庭湾国际大酒店</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>海山路2号</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>1.5: 后厨区摆放可回收物、厨余垃圾、其他垃圾收集容器。（5分） (-5)</t>
+        </is>
+      </c>
+      <c r="O156" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E5%B1%B1%E8%B7%AF2%E5%8F%B7_%E9%9B%85%E5%BA%AD%E6%B9%BE%E5%9B%BD%E9%99%85%E5%A4%A7%E9%85%92%E5%BA%97.html","查看证据(1项/3张)")</f>
+        <v>查看证据(1项/3张)</v>
+      </c>
+      <c r="P156" t="n">
+        <v>95</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>东方二六大厦</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>松岗街道</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>深圳市宝安区松岗街道东方二六大厦</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-2)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O157" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E4%BA%8C%E5%85%AD%E5%A4%A7%E5%8E%A6_%E4%B8%9C%E6%96%B9%E4%BA%8C%E5%85%AD%E5%A4%A7%E5%8E%A6.html","查看证据(3项/4张)")</f>
+        <v>查看证据(3项/4张)</v>
+      </c>
+      <c r="P157" t="n">
+        <v>94</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>六队商住楼</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>松岗街道</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>东方社区</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>深圳市宝安区松岗街道东方社区六队商住楼</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.11: 禁止车辆挡住投放点过道，禁止在投放口前堆放大件杂物。（4分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+4.1: 小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O158" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC_%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC.html","查看证据(5项/7张)")</f>
+        <v>查看证据(5项/7张)</v>
+      </c>
+      <c r="P158" t="n">
+        <v>90</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>松岗街道</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>深圳市宝安区松岗街道东方大道88号旁巷道</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-4)
+1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-4)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分） (-3)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-5)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+4.1: 小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O159" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据(9项/17张)")</f>
+        <v>查看证据(9项/17张)</v>
+      </c>
+      <c r="P159" t="n">
+        <v>74</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>四队</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>松岗街道</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>东方社区</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>深圳市宝安区松岗街道东方社区四队</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+4.1: 小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O160" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%9B%9B%E9%98%9F_%E5%9B%9B%E9%98%9F.html","查看证据(5项/5张)")</f>
+        <v>查看证据(5项/5张)</v>
+      </c>
+      <c r="P160" t="n">
+        <v>90</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:44:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>松岗街道</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>深圳市宝安区松岗街道东方大道75号</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-2)
+1.18: 禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分） (-5)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+4.1: 小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O161" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据(8项/13张)")</f>
+        <v>查看证据(8项/13张)</v>
+      </c>
+      <c r="P161" t="n">
+        <v>81</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:44:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>三队</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>松岗街道</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>东方社区</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>广东省深圳市宝安区松岗街道松岗街道东方社区三队</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+4.1: 小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O162" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E4%B8%89%E9%98%9F_%E4%B8%89%E9%98%9F.html","查看证据(7项/11张)")</f>
+        <v>查看证据(7项/11张)</v>
+      </c>
+      <c r="P162" t="n">
+        <v>86</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:42:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>二队</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>松岗街道</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>深圳市宝安区松岗街道东方大村57号</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>2.1: 设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+2.3: 各类垃圾及时清运。（2分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+4.1: 小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O163" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E6%9D%9157%E5%8F%B7_%E4%BA%8C%E9%98%9F.html","查看证据(5项/6张)")</f>
+        <v>查看证据(5项/6张)</v>
+      </c>
+      <c r="P163" t="n">
+        <v>90</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:42:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>鸿盛花园</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>宝安区</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>深圳市宝安区松岗镇水围村鸿盛花园</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>1.5: 分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分） (-2)
+1.6: 设置洗手设施。（2分） (-1)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)</t>
+        </is>
+      </c>
+      <c r="O164" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B0%B4%E5%9B%B4%E6%9D%91%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD_%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD.html","查看证据(4项/8张)")</f>
+        <v>查看证据(4项/8张)</v>
+      </c>
+      <c r="P164" t="n">
+        <v>91</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:42:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>一致春晓苑</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>罗湖区</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>深圳市罗湖区东晓路4003号</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>1.6: 设置洗手设施。（2分） (-1)
+1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)
+4.4: 设备及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O165" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF4003%E5%8F%B7_%E4%B8%80%E8%87%B4%E6%98%A5%E6%99%93%E8%8B%91.html","查看证据(5项/7张)")</f>
+        <v>查看证据(5项/7张)</v>
+      </c>
+      <c r="P165" t="n">
+        <v>89</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:45:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>泰和花园</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>罗湖区</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>东晓街道</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>广东省深圳市罗湖区-东晓街道东晓路4005号(布心地铁站A口步行280米)</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>1.13: 收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分） (-4)
+3.2: 暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分） (-2)
+4.4: 设备及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O166" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA_%E4%B8%9C%E6%99%93%E8%A1%97%E9%81%93%E4%B8%9C%E6%99%93%E8%B7%AF4005%E5%8F%B7_%E5%B8%83%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C280%E7%B1%B3_%E6%B3%B0%E5%92%8C%E8%8A%B1%E5%9B%AD.html","查看证据(3项/8张)")</f>
+        <v>查看证据(3项/8张)</v>
+      </c>
+      <c r="P166" t="n">
+        <v>92</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:46:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>特力布心工业区</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>罗湖区</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>深圳市罗湖区东晓路3001号布心工业区</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>1.6: 设置洗手设施。（2分） (-1)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)
+2.2: 设置消防设施，使用功能正常，取用方便。（2分） (-2)
+5.4: 回收箱使用功能正常，外观没有严重破损。（1分） (-1)</t>
+        </is>
+      </c>
+      <c r="O167" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF3001%E5%8F%B7%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E7%89%B9%E5%8A%9B%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA.html","查看证据(4项/6张)")</f>
+        <v>查看证据(4项/6张)</v>
+      </c>
+      <c r="P167" t="n">
+        <v>94</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:46:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>东晓花园</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>罗湖区</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>深圳市罗湖区东晓路2001号</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>1.9: 各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+1.16: 禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分） (-2)
+1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-4)</t>
+        </is>
+      </c>
+      <c r="O168" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF2001%E5%8F%B7_%E4%B8%9C%E6%99%93%E8%8A%B1%E5%9B%AD.html","查看证据(4项/5张)")</f>
+        <v>查看证据(4项/5张)</v>
+      </c>
+      <c r="P168" t="n">
+        <v>90</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:46:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>金迪名苑</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>罗湖区</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>深圳市罗湖区东昌路2号</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)</t>
+        </is>
+      </c>
+      <c r="O169" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%98%8C%E8%B7%AF2%E5%8F%B7_%E9%87%91%E8%BF%AA%E5%90%8D%E8%8B%91.html","查看证据(2项/2张)")</f>
+        <v>查看证据(2项/2张)</v>
+      </c>
+      <c r="P169" t="n">
+        <v>96</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:46:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>布心外贸小区</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>罗湖区</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>深圳市罗湖区布心路2038号</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>1.8: 设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分） (-2)
+1.14: 各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分） (-2)
+2.4: 暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分） (-2)</t>
+        </is>
+      </c>
+      <c r="O170" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%B8%83%E5%BF%83%E8%B7%AF2038%E5%8F%B7_%E5%B8%83%E5%BF%83%E5%A4%96%E8%B4%B8%E5%B0%8F%E5%8C%BA.html","查看证据(3项/3张)")</f>
+        <v>查看证据(3项/3张)</v>
+      </c>
+      <c r="P170" t="n">
+        <v>94</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:46:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>东盛苑</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>罗湖区</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>深圳市罗湖区东盛路2号</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>1.17: 转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分） (-2)</t>
+        </is>
+      </c>
+      <c r="O171" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E7%9B%9B%E8%B7%AF2%E5%8F%B7_%E4%B8%9C%E7%9B%9B%E8%8B%91.html","查看证据(1项/2张)")</f>
+        <v>查看证据(1项/2张)</v>
+      </c>
+      <c r="P171" t="n">
+        <v>98</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>2026-09-07 17:46:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17363,7 +19094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G445"/>
+  <dimension ref="A1:G551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -33396,6 +35127,3822 @@
         <v>查看证据</v>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>港中旅花园二期</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D446" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F446" s="5" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G446" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%BA%8C%E6%9C%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>港中旅花园二期</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D447" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F447" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G447" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%BA%8C%E6%9C%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>港中旅花园一期</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D448" s="5" t="inlineStr">
+        <is>
+          <t>至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分）</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F448" s="5" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G448" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>港中旅花园一期</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D449" s="5" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F449" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G449" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>港中旅花园一期</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D450" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F450" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G450" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>港中旅花园一期</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D451" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F451" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G451" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>港中旅花园一期</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D452" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F452" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G452" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E5%9B%AD%E8%B7%AF21%E5%8F%B7_%E6%B8%AF%E4%B8%AD%E6%97%85%E8%8A%B1%E5%9B%AD%E4%B8%80%E6%9C%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>俊安苑</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D453" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F453" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G453" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E5%86%9C%E8%BD%A9%E8%B7%AF121%E5%8F%B7_%E4%BF%8A%E5%AE%89%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>龙溪花园</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D454" s="5" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F454" s="5" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（3处问题）</t>
+        </is>
+      </c>
+      <c r="G454" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF38%E5%8F%B7_%E9%BE%99%E6%BA%AA%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>龙溪花园</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D455" s="5" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分）</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F455" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G455" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF38%E5%8F%B7_%E9%BE%99%E6%BA%AA%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>龙溪花园</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D456" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F456" s="5" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G456" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF38%E5%8F%B7_%E9%BE%99%E6%BA%AA%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>龙溪花园</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D457" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F457" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G457" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF38%E5%8F%B7_%E9%BE%99%E6%BA%AA%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>龙溪花园</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="D458" s="5" t="inlineStr">
+        <is>
+          <t>公共区域宣传栏张贴垃圾分类投放指引或宣传海报。（2分）</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F458" s="5" t="inlineStr">
+        <is>
+          <t>（2）未规范张贴垃圾分类宣传海报（海报缺失、内容错误/未更新等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G458" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF38%E5%8F%B7_%E9%BE%99%E6%BA%AA%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>荔林苑</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D459" s="5" t="inlineStr">
+        <is>
+          <t>至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分）</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F459" s="5" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G459" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF8076%E5%8F%B7_%E8%8D%94%E6%9E%97%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>荔林苑</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D460" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F460" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G460" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF8076%E5%8F%B7_%E8%8D%94%E6%9E%97%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>荔林苑</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D461" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F461" s="5" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G461" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF8076%E5%8F%B7_%E8%8D%94%E6%9E%97%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>荔林苑</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D462" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F462" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G462" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF8076%E5%8F%B7_%E8%8D%94%E6%9E%97%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>荔林苑</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D463" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F463" s="5" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G463" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E7%BA%A2%E8%8D%94%E8%A5%BF%E8%B7%AF8076%E5%8F%B7_%E8%8D%94%E6%9E%97%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>香荔花园</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D464" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F464" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G464" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF11%E5%8F%B7_%E9%A6%99%E8%8D%94%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>海天一色</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D465" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F465" s="5" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G465" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF8%E5%8F%B7_%E6%B5%B7%E5%A4%A9%E4%B8%80%E8%89%B2.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>海天一色</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D466" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F466" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G466" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF8%E5%8F%B7_%E6%B5%B7%E5%A4%A9%E4%B8%80%E8%89%B2.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>海天一色</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D467" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F467" s="5" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G467" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF8%E5%8F%B7_%E6%B5%B7%E5%A4%A9%E4%B8%80%E8%89%B2.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>香蜜天宝物华家园</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="D468" s="5" t="inlineStr">
+        <is>
+          <t>至少设置一处厨余垃圾误时投放点，张贴误时投放点标识，并保持24小时开放。（2分）</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F468" s="5" t="inlineStr">
+        <is>
+          <t>否(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G468" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF3%E5%8F%B7_%E9%A6%99%E8%9C%9C%E5%A4%A9%E5%AE%9D%E7%89%A9%E5%8D%8E%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>香蜜天宝物华家园</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D469" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F469" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G469" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF3%E5%8F%B7_%E9%A6%99%E8%9C%9C%E5%A4%A9%E5%AE%9D%E7%89%A9%E5%8D%8E%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>香蜜天宝物华家园</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="D470" s="5" t="inlineStr">
+        <is>
+          <t>回收箱及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分）</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F470" s="5" t="inlineStr">
+        <is>
+          <t>周边环境脏乱(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G470" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%A6%8F%E7%94%B0%E5%8C%BA%E4%B8%B0%E7%94%B0%E8%B7%AF3%E5%8F%B7_%E9%A6%99%E8%9C%9C%E5%A4%A9%E5%AE%9D%E7%89%A9%E5%8D%8E%E5%AE%B6%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>君临海域</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D471" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F471" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G471" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1015%E5%8F%B7_%E5%90%9B%E4%B8%B4%E6%B5%B7%E5%9F%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>君临海域</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D472" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F472" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G472" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1015%E5%8F%B7_%E5%90%9B%E4%B8%B4%E6%B5%B7%E5%9F%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>君临海域</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D473" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F473" s="5" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G473" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1015%E5%8F%B7_%E5%90%9B%E4%B8%B4%E6%B5%B7%E5%9F%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>滨海花园</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D474" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F474" s="5" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G474" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B5%B7%E6%99%AF%E8%B7%AF1%E5%8F%B7_%E6%BB%A8%E6%B5%B7%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>壹海城</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D475" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F475" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G475" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E7%9B%90%E7%94%B0%E5%8C%BA%E6%B7%B1%E7%9B%90%E8%B7%AF%E4%B8%8E%E9%A9%AC%E5%BA%99%E7%AD%89%E4%BA%A4%E6%B1%87%E5%A4%84_%E5%A3%B9%E6%B5%B7%E5%9F%8E.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>壹海城V公馆</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D476" s="5" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F476" s="5" t="inlineStr">
+        <is>
+          <t>（3）外罩和内桶颜色不正确;（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G476" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1038%E5%8F%B7_%E5%A3%B9%E6%B5%B7%E5%9F%8EV%E5%85%AC%E9%A6%86.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>壹海城V公馆</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D477" s="5" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F477" s="5" t="inlineStr">
+        <is>
+          <t>（2）洗手设施缺失(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G477" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1038%E5%8F%B7_%E5%A3%B9%E6%B5%B7%E5%9F%8EV%E5%85%AC%E9%A6%86.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>壹海城V公馆</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D478" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F478" s="5" t="inlineStr">
+        <is>
+          <t>（3）无标识牌，或标识牌被遮挡、模糊/脱落/未更新等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G478" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1038%E5%8F%B7_%E5%A3%B9%E6%B5%B7%E5%9F%8EV%E5%85%AC%E9%A6%86.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>壹海城V公馆</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D479" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F479" s="5" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G479" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E6%99%AF%E4%BA%8C%E8%B7%AF1038%E5%8F%B7_%E5%A3%B9%E6%B5%B7%E5%9F%8EV%E5%85%AC%E9%A6%86.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>餐饮场所</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>八合里</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D480" s="5" t="inlineStr">
+        <is>
+          <t>后厨区摆放可回收物、厨余垃圾、其他垃圾收集容器。（6分）</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="F480" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-6)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G480" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E5%B1%B1%E8%B7%AF%E5%8C%97%E9%9D%A2%E5%A3%B9%E6%B5%B7MALL%E5%9B%9B%E5%B1%82001%E5%8F%B7_%E5%85%AB%E5%90%88%E9%87%8C.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>餐饮场所</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>八合里</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="D481" s="5" t="inlineStr">
+        <is>
+          <t>各类收集容器的分类标志完整、正确、清晰。 （18分）</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F481" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器标志缺失、错误或模糊不清的。（不强制要求垃圾桶套袋，若套袋的，收集容器应按垃圾类别对应颜色套袋）(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G481" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E5%B1%B1%E8%B7%AF%E5%8C%97%E9%9D%A2%E5%A3%B9%E6%B5%B7MALL%E5%9B%9B%E5%B1%82001%E5%8F%B7_%E5%85%AB%E5%90%88%E9%87%8C.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>购物中心</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>华润万家超市</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D482" s="5" t="inlineStr">
+        <is>
+          <t>收集容器、暂存点及其周围环境干净整洁，无垃圾满溢、暴露垃圾，无杂物堆放。</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F482" s="5" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有散落垃圾、杂物堆放，地面有明显污水污渍）(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G482" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E7%9B%90%E8%B7%AF%E4%B8%8E%E6%B5%B7%E5%B1%B1%E8%B7%AF%E4%BA%A4%E6%B1%87%E5%A4%84%E5%A3%B9%E6%B5%B7%E9%81%93B1_%E5%8D%8E%E6%B6%A6%E4%B8%87%E5%AE%B6%E8%B6%85%E5%B8%82.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>酒店</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>雅庭湾国际大酒店</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D483" s="5" t="inlineStr">
+        <is>
+          <t>后厨区摆放可回收物、厨余垃圾、其他垃圾收集容器。（5分）</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F483" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器缺失(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G483" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B5%B7%E5%B1%B1%E8%B7%AF2%E5%8F%B7_%E9%9B%85%E5%BA%AD%E6%B9%BE%E5%9B%BD%E9%99%85%E5%A4%A7%E9%85%92%E5%BA%97.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>东方二六大厦</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D484" s="5" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分）</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F484" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G484" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E4%BA%8C%E5%85%AD%E5%A4%A7%E5%8E%A6_%E4%B8%9C%E6%96%B9%E4%BA%8C%E5%85%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>东方二六大厦</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D485" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F485" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G485" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E4%BA%8C%E5%85%AD%E5%A4%A7%E5%8E%A6_%E4%B8%9C%E6%96%B9%E4%BA%8C%E5%85%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>东方二六大厦</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D486" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F486" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G486" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E4%BA%8C%E5%85%AD%E5%A4%A7%E5%8E%A6_%E4%B8%9C%E6%96%B9%E4%BA%8C%E5%85%AD%E5%A4%A7%E5%8E%A6.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>六队商住楼</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D487" s="5" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F487" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G487" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC_%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>六队商住楼</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="D488" s="5" t="inlineStr">
+        <is>
+          <t>禁止车辆挡住投放点过道，禁止在投放口前堆放大件杂物。（4分）</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F488" s="5" t="inlineStr">
+        <is>
+          <t>（2）车辆挡住投放点过道、投放口前堆放大件杂物，阻碍居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G488" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC_%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>六队商住楼</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D489" s="5" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F489" s="5" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G489" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC_%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>六队商住楼</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D490" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F490" s="5" t="inlineStr">
+        <is>
+          <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G490" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC_%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>六队商住楼</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="D491" s="5" t="inlineStr">
+        <is>
+          <t>小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分）</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F491" s="5" t="inlineStr">
+        <is>
+          <t>（2）存在超过3家(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G491" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC_%E5%85%AD%E9%98%9F%E5%95%86%E4%BD%8F%E6%A5%BC.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D492" s="5" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F492" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）； （4）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G492" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D493" s="5" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分）</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F493" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G493" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D494" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（6分）</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="F494" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-3)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G494" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D495" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F495" s="5" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G495" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D496" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F496" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G496" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="D497" s="5" t="inlineStr">
+        <is>
+          <t>禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分）</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F497" s="5" t="inlineStr">
+        <is>
+          <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G497" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D498" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F498" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G498" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D499" s="5" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F499" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G499" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>六队</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="D500" s="5" t="inlineStr">
+        <is>
+          <t>小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分）</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F500" s="5" t="inlineStr">
+        <is>
+          <t>（2）存在超过3家(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G500" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9388%E5%8F%B7%E6%97%81%E5%B7%B7%E9%81%93_%E5%85%AD%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>四队</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D501" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F501" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G501" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%9B%9B%E9%98%9F_%E5%9B%9B%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>四队</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D502" s="5" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F502" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G502" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%9B%9B%E9%98%9F_%E5%9B%9B%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>四队</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D503" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F503" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G503" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%9B%9B%E9%98%9F_%E5%9B%9B%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>四队</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D504" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F504" s="5" t="inlineStr">
+        <is>
+          <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G504" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%9B%9B%E9%98%9F_%E5%9B%9B%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>四队</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="D505" s="5" t="inlineStr">
+        <is>
+          <t>小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分）</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F505" s="5" t="inlineStr">
+        <is>
+          <t>（2）存在超过3家(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G505" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E5%9B%9B%E9%98%9F_%E5%9B%9B%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D506" s="5" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F506" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G506" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D507" s="5" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分）</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F507" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类设施损坏或摆放不整齐(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G507" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="D508" s="5" t="inlineStr">
+        <is>
+          <t>禁止在楼层、地面或车库等设置分散式垃圾收集容器。（4分）</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="F508" s="5" t="inlineStr">
+        <is>
+          <t>（2）设置分散式垃圾收集容器（随意摆桶未划黄线）(-5)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G508" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D509" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F509" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G509" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D510" s="5" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F510" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G510" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D511" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F511" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G511" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D512" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F512" s="5" t="inlineStr">
+        <is>
+          <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G512" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>八队</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="D513" s="5" t="inlineStr">
+        <is>
+          <t>小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分）</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F513" s="5" t="inlineStr">
+        <is>
+          <t>（2）存在超过3家(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G513" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E9%81%9375%E5%8F%B7_%E5%85%AB%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>三队</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D514" s="5" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F514" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G514" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E4%B8%89%E9%98%9F_%E4%B8%89%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>三队</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D515" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F515" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G515" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E4%B8%89%E9%98%9F_%E4%B8%89%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>三队</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D516" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F516" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G516" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E4%B8%89%E9%98%9F_%E4%B8%89%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>三队</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D517" s="5" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F517" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G517" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E4%B8%89%E9%98%9F_%E4%B8%89%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>三队</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D518" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F518" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G518" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E4%B8%89%E9%98%9F_%E4%B8%89%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>三队</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D519" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F519" s="5" t="inlineStr">
+        <is>
+          <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G519" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E4%B8%89%E9%98%9F_%E4%B8%89%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>三队</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="D520" s="5" t="inlineStr">
+        <is>
+          <t>小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分）</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F520" s="5" t="inlineStr">
+        <is>
+          <t>（2）存在超过3家(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G520" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E7%A4%BE%E5%8C%BA%E4%B8%89%E9%98%9F_%E4%B8%89%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>二队</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D521" s="5" t="inlineStr">
+        <is>
+          <t>设置标识牌，外观使用“深i回收”标识，封闭围挡，地面硬底化。（2分）</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F521" s="5" t="inlineStr">
+        <is>
+          <t>（5）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G521" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E6%9D%9157%E5%8F%B7_%E4%BA%8C%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>二队</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D522" s="5" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F522" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G522" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E6%9D%9157%E5%8F%B7_%E4%BA%8C%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>二队</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="D523" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运。（2分）</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F523" s="5" t="inlineStr">
+        <is>
+          <t>（3）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G523" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E6%9D%9157%E5%8F%B7_%E4%BA%8C%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>二队</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D524" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F524" s="5" t="inlineStr">
+        <is>
+          <t>（7）其他问题说明（备注描述）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G524" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E6%9D%9157%E5%8F%B7_%E4%BA%8C%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>城中村</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>二队</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="D525" s="5" t="inlineStr">
+        <is>
+          <t>小区内设置废旧织物回收箱的企业数量原则上不超过3家。（2分）</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F525" s="5" t="inlineStr">
+        <is>
+          <t>（2）存在超过3家(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G525" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E8%A1%97%E9%81%93%E4%B8%9C%E6%96%B9%E5%A4%A7%E6%9D%9157%E5%8F%B7_%E4%BA%8C%E9%98%9F.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>鸿盛花园</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D526" s="5" t="inlineStr">
+        <is>
+          <t>分类标志完整、正确、清晰，各类垃圾收集容器外罩和内桶的颜色正确。（4分）</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F526" s="5" t="inlineStr">
+        <is>
+          <t>（2）分类桶标志缺失或不规范（标志未更新、标志错误、标志模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G526" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B0%B4%E5%9B%B4%E6%9D%91%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD_%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>鸿盛花园</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D527" s="5" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F527" s="5" t="inlineStr">
+        <is>
+          <t>（2）洗手设施缺失(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G527" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B0%B4%E5%9B%B4%E6%9D%91%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD_%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>鸿盛花园</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D528" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F528" s="5" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G528" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B0%B4%E5%9B%B4%E6%9D%91%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD_%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>鸿盛花园</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D529" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F529" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G529" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E5%AE%9D%E5%AE%89%E5%8C%BA%E6%9D%BE%E5%B2%97%E9%95%87%E6%B0%B4%E5%9B%B4%E6%9D%91%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD_%E9%B8%BF%E7%9B%9B%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>一致春晓苑</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D530" s="5" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F530" s="5" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G530" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF4003%E5%8F%B7_%E4%B8%80%E8%87%B4%E6%98%A5%E6%99%93%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>一致春晓苑</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D531" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F531" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G531" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF4003%E5%8F%B7_%E4%B8%80%E8%87%B4%E6%98%A5%E6%99%93%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>一致春晓苑</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D532" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F532" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G532" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF4003%E5%8F%B7_%E4%B8%80%E8%87%B4%E6%98%A5%E6%99%93%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>一致春晓苑</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D533" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F533" s="5" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G533" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF4003%E5%8F%B7_%E4%B8%80%E8%87%B4%E6%98%A5%E6%99%93%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>一致春晓苑</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="D534" s="5" t="inlineStr">
+        <is>
+          <t>设备及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分）</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F534" s="5" t="inlineStr">
+        <is>
+          <t>（1）存在问题(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G534" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF4003%E5%8F%B7_%E4%B8%80%E8%87%B4%E6%98%A5%E6%99%93%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>泰和花园</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="D535" s="5" t="inlineStr">
+        <is>
+          <t>收集容器外壁及内桶保持干净整洁，避免陈旧性脏污，收集容器内无积水。（4分）</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F535" s="5" t="inlineStr">
+        <is>
+          <t>（2）收集容器外壁、内桶存在明显陈旧性脏污，大片锈迹等(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G535" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA_%E4%B8%9C%E6%99%93%E8%A1%97%E9%81%93%E4%B8%9C%E6%99%93%E8%B7%AF4005%E5%8F%B7_%E5%B8%83%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C280%E7%B1%B3_%E6%B3%B0%E5%92%8C%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>泰和花园</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D536" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，各类桶整齐、密闭摆放，没有污水积聚或散落垃圾。（2分）</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F536" s="5" t="inlineStr">
+        <is>
+          <t>（2）暂存点及周围环境不整洁（垃圾堆放杂乱、垃圾散落、地面污水积聚等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G536" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA_%E4%B8%9C%E6%99%93%E8%A1%97%E9%81%93%E4%B8%9C%E6%99%93%E8%B7%AF4005%E5%8F%B7_%E5%B8%83%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C280%E7%B1%B3_%E6%B3%B0%E5%92%8C%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>泰和花园</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="D537" s="5" t="inlineStr">
+        <is>
+          <t>设备及周边环境干净整洁，无垃圾满溢、暴露垃圾或杂物堆放等问题。（2分）</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F537" s="5" t="inlineStr">
+        <is>
+          <t>（1）存在问题(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G537" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E5%B9%BF%E4%B8%9C%E7%9C%81%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA_%E4%B8%9C%E6%99%93%E8%A1%97%E9%81%93%E4%B8%9C%E6%99%93%E8%B7%AF4005%E5%8F%B7_%E5%B8%83%E5%BF%83%E5%9C%B0%E9%93%81%E7%AB%99A%E5%8F%A3%E6%AD%A5%E8%A1%8C280%E7%B1%B3_%E6%B3%B0%E5%92%8C%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>特力布心工业区</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D538" s="5" t="inlineStr">
+        <is>
+          <t>设置洗手设施。（2分）</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F538" s="5" t="inlineStr">
+        <is>
+          <t>（3）洗手设施不规范（包括水龙头损坏或明显松动，水龙头不出水，洗手盆堵塞等）(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G538" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF3001%E5%8F%B7%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E7%89%B9%E5%8A%9B%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>特力布心工业区</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D539" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F539" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G539" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF3001%E5%8F%B7%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E7%89%B9%E5%8A%9B%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>特力布心工业区</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="D540" s="5" t="inlineStr">
+        <is>
+          <t>设置消防设施，使用功能正常，取用方便。（2分）</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F540" s="5" t="inlineStr">
+        <is>
+          <t>（2）消防设施不规范（设备缺失、破损严重/过期等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G540" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF3001%E5%8F%B7%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E7%89%B9%E5%8A%9B%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>特力布心工业区</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="D541" s="5" t="inlineStr">
+        <is>
+          <t>回收箱使用功能正常，外观没有严重破损。（1分）</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="F541" s="5" t="inlineStr">
+        <is>
+          <t>存在严重破损(-1)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G541" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF3001%E5%8F%B7%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA_%E7%89%B9%E5%8A%9B%E5%B8%83%E5%BF%83%E5%B7%A5%E4%B8%9A%E5%8C%BA.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>东晓花园</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="D542" s="5" t="inlineStr">
+        <is>
+          <t>各设施齐全完好，摆放整齐有序，使用功能正常，没有严重破损、陈旧问题，不得拆除投放口盖板支撑杆。（6分）</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F542" s="5" t="inlineStr">
+        <is>
+          <t>（3）内桶错放导致桶盖无法正常打开，未放置垃圾内桶等影响正常使用(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G542" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF2001%E5%8F%B7_%E4%B8%9C%E6%99%93%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>东晓花园</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D543" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F543" s="5" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G543" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF2001%E5%8F%B7_%E4%B8%9C%E6%99%93%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>东晓花园</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="D544" s="5" t="inlineStr">
+        <is>
+          <t>禁止通过捆绑、卡挡或上锁等方式封闭或遮挡投放口。（4分）</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F544" s="5" t="inlineStr">
+        <is>
+          <t>（4）误时投放点未开放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G544" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF2001%E5%8F%B7_%E4%B8%9C%E6%99%93%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>东晓花园</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D545" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="F545" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（2处问题）</t>
+        </is>
+      </c>
+      <c r="G545" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%99%93%E8%B7%AF2001%E5%8F%B7_%E4%B8%9C%E6%99%93%E8%8A%B1%E5%9B%AD.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>金迪名苑</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D546" s="5" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F546" s="5" t="inlineStr">
+        <is>
+          <t>（2）责任公示牌缺失(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G546" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%98%8C%E8%B7%AF2%E5%8F%B7_%E9%87%91%E8%BF%AA%E5%90%8D%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>金迪名苑</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D547" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F547" s="5" t="inlineStr">
+        <is>
+          <t>（3）环境卫生不整洁（投放点有暴露垃圾、杂物堆放，洗手池严重脏污，地面未硬底化，有明显污水污渍等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G547" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E6%98%8C%E8%B7%AF2%E5%8F%B7_%E9%87%91%E8%BF%AA%E5%90%8D%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>布心外贸小区</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="D548" s="5" t="inlineStr">
+        <is>
+          <t>设置公示牌，清晰公示管理责任人和电话、专项垃圾暂存点和废旧织物回收箱位置、厨余垃圾投放时段、各类垃圾收运处理企业等信息。（4分）</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F548" s="5" t="inlineStr">
+        <is>
+          <t>（3）公示牌设置不规范（公示牌脱落、内容缺失、错误或模糊等）(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G548" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%B8%83%E5%BF%83%E8%B7%AF2038%E5%8F%B7_%E5%B8%83%E5%BF%83%E5%A4%96%E8%B4%B8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>布心外贸小区</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="D549" s="5" t="inlineStr">
+        <is>
+          <t>各类垃圾及时清运，投放点及其周围环境干净整洁，没有垃圾满溢、暴露垃圾、杂物堆放、严重积水或明显异味等问题。（6分）</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F549" s="5" t="inlineStr">
+        <is>
+          <t>（2）垃圾收集容器满溢、未及时清运(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G549" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%B8%83%E5%BF%83%E8%B7%AF2038%E5%8F%B7_%E5%B8%83%E5%BF%83%E5%A4%96%E8%B4%B8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>布心外贸小区</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="D550" s="5" t="inlineStr">
+        <is>
+          <t>暂存点及其周围环境干净整洁，没有污水积聚或散落垃圾，禁止存放易燃易爆危险品，禁止违规接电、住人。（2分）</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F550" s="5" t="inlineStr">
+        <is>
+          <t>（4）暂存点外堆放废旧家具等大件垃圾(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G550" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E5%B8%83%E5%BF%83%E8%B7%AF2038%E5%8F%B7_%E5%B8%83%E5%BF%83%E5%A4%96%E8%B4%B8%E5%B0%8F%E5%8C%BA.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>住宅小区</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>东盛苑</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="D551" s="5" t="inlineStr">
+        <is>
+          <t>转运桶应在黄线划定区域内摆放整齐并保持全天关闭（作业状态除外），禁止罩外摆桶供居民投放。（6分）</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="F551" s="5" t="inlineStr">
+        <is>
+          <t>（3）监控范围外罩外摆桶并开盖供居民投放(-2)（1处问题）</t>
+        </is>
+      </c>
+      <c r="G551" t="str">
+        <f>HYPERLINK("https://yueling-buddy.github.io/xxr-inspection-album/weeks/2026-09-03/venue/v-%E6%B7%B1%E5%9C%B3%E5%B8%82%E7%BD%97%E6%B9%96%E5%8C%BA%E4%B8%9C%E7%9B%9B%E8%B7%AF2%E5%8F%B7_%E4%B8%9C%E7%9B%9B%E8%8B%91.html","查看证据")</f>
+        <v>查看证据</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/weeks/2026-09-03/巡查表.xlsx
+++ b/weeks/2026-09-03/巡查表.xlsx
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/2张)</t>
+          <t>查看证据(1项/1张)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>查看证据(2项/4张)</t>
+          <t>查看证据(2项/2张)</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/2张)</t>
+          <t>查看证据(1项/1张)</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/2张)</t>
+          <t>查看证据(1项/1张)</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>查看证据(2项/6张)</t>
+          <t>查看证据(2项/4张)</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -13825,7 +13825,7 @@
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/7张)</t>
+          <t>查看证据(1项/4张)</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>查看证据(4项/10张)</t>
+          <t>查看证据(4项/5张)</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>查看证据(3项/10张)</t>
+          <t>查看证据(3项/6张)</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>查看证据(2项/5张)</t>
+          <t>查看证据(2项/3张)</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/2张)</t>
+          <t>查看证据(1项/1张)</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>查看证据(3项/9张)</t>
+          <t>查看证据(3项/6张)</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>查看证据(2项/4张)</t>
+          <t>查看证据(2项/2张)</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>查看证据(2项/5张)</t>
+          <t>查看证据(2项/3张)</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/2张)</t>
+          <t>查看证据(1项/1张)</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/4张)</t>
+          <t>查看证据(1项/2张)</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>查看证据(3项/8张)</t>
+          <t>查看证据(3项/4张)</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>查看证据(3项/6张)</t>
+          <t>查看证据(3项/3张)</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>查看证据(3项/7张)</t>
+          <t>查看证据(3项/4张)</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -18043,7 +18043,7 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/4张)</t>
+          <t>查看证据(1项/2张)</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/2张)</t>
+          <t>查看证据(1项/1张)</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>查看证据(4项/8张)</t>
+          <t>查看证据(4项/4张)</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>查看证据(2项/5张)</t>
+          <t>查看证据(2项/3张)</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -18252,7 +18252,7 @@
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/2张)</t>
+          <t>查看证据(1项/1张)</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -18302,7 +18302,7 @@
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/3张)</t>
+          <t>查看证据(1项/2张)</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>查看证据(3项/8张)</t>
+          <t>查看证据(3项/4张)</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -19235,7 +19235,7 @@
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>查看证据(1项/2张)</t>
+          <t>查看证据(1项/1张)</t>
         </is>
       </c>
       <c r="P171" t="n">
